--- a/risultati_dettagliati_microgrid.xlsx
+++ b/risultati_dettagliati_microgrid.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z97"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,70 +479,85 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>H2_flow_EL</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>H2_flow_H2S</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>H2_flow_H2V</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>CargoBike_1_SOC_kg</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CargoBike_1_SOC_Percent</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>CargoBike_2_SOC_kg</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>CargoBike_2_SOC_Percent</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CargoBike_3_SOC_kg</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>CargoBike_3_SOC_Percent</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>CargoBike_4_SOC_kg</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>CargoBike_4_SOC_Percent</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CargoBike_5_SOC_kg</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>CargoBike_5_SOC_Percent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Forklift_1_SOC_kg</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Forklift_1_SOC_Percent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Forklift_2_SOC_kg</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Forklift_2_SOC_Percent</t>
         </is>
@@ -551,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -570,16 +585,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -597,71 +612,80 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1</v>
+        <v>5.63</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.6640792</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.6640792</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>500</v>
+        <v>14.6524356</v>
       </c>
       <c r="J3" t="n">
-        <v>33.33333333333333</v>
+        <v>0.97682904</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -670,80 +694,89 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>58.6097424</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>-58.6097424</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3052777777777778</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01695987654320988</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0542929292929293</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0542929292929293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.84</v>
+        <v>6.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.429473742</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.429473742</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>500</v>
+        <v>33.514541181</v>
       </c>
       <c r="J4" t="n">
-        <v>33.33333333333333</v>
+        <v>2.2343027454</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -752,80 +785,89 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>75.44842232399999</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>-75.44842232399999</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3327777777777778</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01848765432098766</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.05303030303030304</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.05303030303030304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.31</v>
+        <v>6.21</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.948779808</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3.948779808</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>500</v>
+        <v>55.23283012499999</v>
       </c>
       <c r="J5" t="n">
-        <v>33.33333333333333</v>
+        <v>3.682188675</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -834,80 +876,89 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>86.87315577599999</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>-86.87315577599999</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3602777777777778</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02001543209876543</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.9318181818181819</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.9318181818181819</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.05176767676767677</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9318181818181819</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.05176767676767677</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.52</v>
+        <v>8.08</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.585746438</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4.585746438</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>500</v>
+        <v>80.454435534</v>
       </c>
       <c r="J6" t="n">
-        <v>33.33333333333333</v>
+        <v>5.3636290356</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -916,80 +967,89 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>100.886421636</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>-100.886421636</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3877777777777778</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02154320987654321</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0505050505050505</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.0505050505050505</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.34</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5.263484598</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5.263484598</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>500</v>
+        <v>109.403600823</v>
       </c>
       <c r="J7" t="n">
-        <v>33.33333333333333</v>
+        <v>7.2935733882</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -998,80 +1058,89 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>115.796661156</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>-115.796661156</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4152777777777779</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02307098765432099</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.8863636363636365</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>0.8863636363636365</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.04924242424242425</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8863636363636365</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.04924242424242425</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.31</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5.763834048</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5.763834048</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>500</v>
+        <v>141.104688087</v>
       </c>
       <c r="J8" t="n">
-        <v>33.33333333333333</v>
+        <v>9.406979205799999</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1080,80 +1149,89 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>126.804349056</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>-126.804349056</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0.8636363636363638</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0.8636363636363639</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0.8636363636363638</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.8636363636363639</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.8636363636363638</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0.8636363636363639</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0.8636363636363638</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4427777777777779</v>
+        <v>0.8636363636363639</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02459876543209877</v>
+        <v>0.8636363636363638</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.8636363636363639</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>0.8636363636363638</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.04797979797979798</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8636363636363638</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.04797979797979798</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.57</v>
+        <v>8.25</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6.085242432</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6.085242432</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>500</v>
+        <v>174.573521463</v>
       </c>
       <c r="J9" t="n">
-        <v>33.33333333333333</v>
+        <v>11.6382347642</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1162,80 +1240,89 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>133.875333504</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>-133.875333504</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.8409090909090911</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.8409090909090912</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0.8409090909090911</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.8409090909090912</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.8409090909090911</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0.8409090909090912</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0.8409090909090911</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4702777777777779</v>
+        <v>0.8409090909090912</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02612654320987655</v>
+        <v>0.8409090909090911</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.8409090909090912</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>0.8409090909090911</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.04671717171717173</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8409090909090911</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.04671717171717173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2</v>
+        <v>8.65</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6.597341838</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>6.597341838</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>500</v>
+        <v>210.858901572</v>
       </c>
       <c r="J10" t="n">
-        <v>33.33333333333333</v>
+        <v>14.0572601048</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1244,80 +1331,89 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>145.141520436</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>-145.141520436</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0.8181818181818185</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.8181818181818185</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0.8181818181818185</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4977777777777779</v>
+        <v>0.8181818181818185</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02765432098765433</v>
+        <v>0.8181818181818183</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.8181818181818185</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>0.8181818181818183</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8181818181818183</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.04545454545454546</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.41</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>7.112685077999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>7.112685077999999</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>500</v>
+        <v>249.978669501</v>
       </c>
       <c r="J11" t="n">
-        <v>33.33333333333333</v>
+        <v>16.6652446334</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1326,80 +1422,89 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>156.479071716</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>-156.479071716</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.7954545454545456</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.7954545454545457</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0.7954545454545456</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.7954545454545457</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.7954545454545456</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0.7954545454545457</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.7954545454545456</v>
       </c>
       <c r="W11" t="n">
-        <v>0.525277777777778</v>
+        <v>0.7954545454545457</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02918209876543211</v>
+        <v>0.7954545454545456</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.7954545454545457</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>0.7954545454545456</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0441919191919192</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7954545454545456</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.0441919191919192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7.492560408</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>7.492560408</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>500</v>
+        <v>291.187751745</v>
       </c>
       <c r="J12" t="n">
-        <v>33.33333333333333</v>
+        <v>19.412516783</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1408,80 +1513,89 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>164.836328976</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>-164.836328976</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5527777777777779</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03070987654320988</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.7727272727272729</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>0.7727272727272729</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.04292929292929294</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.7727272727272729</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.04292929292929294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7</v>
+        <v>8.9</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>7.878090341999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>7.878090341999999</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>500</v>
+        <v>334.517248626</v>
       </c>
       <c r="J13" t="n">
-        <v>33.33333333333333</v>
+        <v>22.3011499084</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1490,80 +1604,89 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>173.317987524</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>-173.317987524</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5802777777777779</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03223765432098766</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.7500000000000002</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>0.7500000000000002</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.04166666666666668</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.7500000000000002</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.04166666666666668</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.28</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>8.338290047999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>8.338290047999999</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>500</v>
+        <v>380.37784389</v>
       </c>
       <c r="J14" t="n">
-        <v>33.33333333333333</v>
+        <v>25.358522926</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1572,80 +1695,89 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>183.442381056</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>-183.442381056</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6077777777777779</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03376543209876544</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.7272727272727275</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>0.7272727272727275</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.04040404040404041</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7272727272727275</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.04040404040404041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5</v>
+        <v>7.57</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>8.478718901999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8.478718901999999</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>500</v>
+        <v>427.010797851</v>
       </c>
       <c r="J15" t="n">
-        <v>33.33333333333333</v>
+        <v>28.4673865234</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1654,80 +1786,89 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>186.531815844</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>-186.531815844</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6352777777777778</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03529320987654321</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.7045454545454548</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.7045454545454548</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.03914141414141416</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7045454545454548</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.03914141414141416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.57</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9.141293502</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.1412935019999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>24.0014718073125</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>0.1471807312499999</v>
       </c>
       <c r="I16" t="n">
-        <v>500</v>
+        <v>476.510797851</v>
       </c>
       <c r="J16" t="n">
-        <v>33.33333333333333</v>
+        <v>31.7673865234</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1736,80 +1877,89 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6627777777777778</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03682098765432099</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.6818181818181821</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>0.6818181818181821</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.03787878787878789</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.6818181818181821</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.03787878787878789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.57</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8.978487462</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>8.978487462</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>24.0014718073125</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>0.1471807312499999</v>
       </c>
       <c r="I17" t="n">
-        <v>500</v>
+        <v>525.892478892</v>
       </c>
       <c r="J17" t="n">
-        <v>33.33333333333333</v>
+        <v>35.0594985928</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1818,80 +1968,89 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>197.526724164</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>-197.526724164</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6902777777777778</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03834876543209877</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.6590909090909094</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>0.6590909090909094</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.03661616161616164</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6590909090909094</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.03661616161616164</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.54</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>9.541429398</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.541429398</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>24.007111696875</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>0.7111696875</v>
       </c>
       <c r="I18" t="n">
-        <v>500</v>
+        <v>575.392478892</v>
       </c>
       <c r="J18" t="n">
-        <v>33.33333333333333</v>
+        <v>38.3594985928</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1900,80 +2059,89 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7177777777777777</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="X18" t="n">
-        <v>0.03987654320987654</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.6363636363636367</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>0.6363636363636367</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.03535353535353537</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.6363636363636367</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.03535353535353537</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.54</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>9.711852552</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.7118525519999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>24.014526827625</v>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>1.4526827625</v>
       </c>
       <c r="I19" t="n">
-        <v>500</v>
+        <v>624.892478892</v>
       </c>
       <c r="J19" t="n">
-        <v>33.33333333333333</v>
+        <v>41.6594985928</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1982,80 +2150,89 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7452777777777777</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="X19" t="n">
-        <v>0.04140432098765432</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.613636363636364</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>0.613636363636364</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.03409090909090911</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.613636363636364</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.03409090909090911</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>9.5629002</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.5629001999999996</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>24.020390371375</v>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>2.039037137499999</v>
       </c>
       <c r="I20" t="n">
-        <v>500</v>
+        <v>674.392478892</v>
       </c>
       <c r="J20" t="n">
-        <v>33.33333333333333</v>
+        <v>44.9594985928</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2064,80 +2241,89 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7727777777777777</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="X20" t="n">
-        <v>0.04293209876543209</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.5909090909090913</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>0.5909090909090913</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.03282828282828285</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.5909090909090913</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.03282828282828285</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.87</v>
+        <v>8.65</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>10.026753192</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1.026753192000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>24.031085717125</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>3.1085717125</v>
       </c>
       <c r="I21" t="n">
-        <v>500</v>
+        <v>723.892478892</v>
       </c>
       <c r="J21" t="n">
-        <v>33.33333333333333</v>
+        <v>48.2594985928</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2146,80 +2332,89 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8002777777777776</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="X21" t="n">
-        <v>0.04445987654320987</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.5681818181818186</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>0.5681818181818186</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.03156565656565658</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5681818181818186</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.03156565656565658</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>8.59</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>10.000384128</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.000384128000002</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>24.041506385125</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>4.150638512500002</v>
       </c>
       <c r="I22" t="n">
-        <v>500</v>
+        <v>773.392478892</v>
       </c>
       <c r="J22" t="n">
-        <v>33.33333333333333</v>
+        <v>51.5594985928</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2228,80 +2423,89 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8277777777777776</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="X22" t="n">
-        <v>0.04598765432098764</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>0.5454545454545459</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>0.5454545454545459</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.03030303030303032</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5454545454545459</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.03030303030303032</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.28</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>9.902930568000002</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.9029305680000022</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>24.050911911875</v>
       </c>
       <c r="H23" t="n">
-        <v>50</v>
+        <v>5.091191187500005</v>
       </c>
       <c r="I23" t="n">
-        <v>500</v>
+        <v>822.892478892</v>
       </c>
       <c r="J23" t="n">
-        <v>33.33333333333333</v>
+        <v>54.8594985928</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2310,80 +2514,89 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8552777777777776</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="X23" t="n">
-        <v>0.04751543209876542</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>0.5227272727272732</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>0.5227272727272732</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.02904040404040406</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.5227272727272732</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.02904040404040406</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.39</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>9.910027782</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.9100277820000002</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>24.0603913679375</v>
       </c>
       <c r="H24" t="n">
-        <v>50</v>
+        <v>6.039136793750005</v>
       </c>
       <c r="I24" t="n">
-        <v>500</v>
+        <v>872.392478892</v>
       </c>
       <c r="J24" t="n">
-        <v>33.33333333333333</v>
+        <v>58.1594985928</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2392,80 +2605,89 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8827777777777776</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0490432098765432</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>0.5000000000000004</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.0277777777777778</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.5000000000000004</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.0277777777777778</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.16</v>
+        <v>8.49</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>10.134611022</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.134611022</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>24.07221023275</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>7.221023275000005</v>
       </c>
       <c r="I25" t="n">
-        <v>500</v>
+        <v>921.892478892</v>
       </c>
       <c r="J25" t="n">
-        <v>33.33333333333333</v>
+        <v>61.4594985928</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2474,80 +2696,89 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9102777777777775</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="X25" t="n">
-        <v>0.05057098765432098</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>0.4772727272727277</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>0.4772727272727277</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.02651515151515154</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4772727272727277</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.02651515151515154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.31</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>9.893447928000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.8934479280000005</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>24.081516982</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>8.151698200000006</v>
       </c>
       <c r="I26" t="n">
-        <v>500</v>
+        <v>971.392478892</v>
       </c>
       <c r="J26" t="n">
-        <v>33.33333333333333</v>
+        <v>64.7594985928</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2556,80 +2787,89 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9377777777777775</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="X26" t="n">
-        <v>0.05209876543209874</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.454545454545455</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.02525252525252528</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.02525252525252528</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.14</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>9.932678861999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.9326788619999995</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>24.0912323868125</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>9.123238681250005</v>
       </c>
       <c r="I27" t="n">
-        <v>500</v>
+        <v>1020.892478892</v>
       </c>
       <c r="J27" t="n">
-        <v>33.33333333333333</v>
+        <v>68.0594985928</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2638,80 +2878,89 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="W27" t="n">
-        <v>0.9652777777777775</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="X27" t="n">
-        <v>0.05362654320987652</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.4318181818181823</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>0.4318181818181823</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.02398989898989902</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4318181818181823</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.02398989898989902</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.35</v>
+        <v>8.57</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6889206480000001</v>
+        <v>9.7100352</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.7100352000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>12</v>
+        <v>24.0986285868125</v>
       </c>
       <c r="H28" t="n">
-        <v>50</v>
+        <v>9.862858681250005</v>
       </c>
       <c r="I28" t="n">
-        <v>500</v>
+        <v>1070.392478892</v>
       </c>
       <c r="J28" t="n">
-        <v>33.33333333333333</v>
+        <v>71.35949859279999</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2720,80 +2969,89 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9927777777777774</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="X28" t="n">
-        <v>0.05515432098765431</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.4090909090909096</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>0.4090909090909096</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.02272727272727276</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.4090909090909096</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.02272727272727276</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.14</v>
+        <v>8.66</v>
       </c>
       <c r="C29" t="n">
-        <v>1.402933752</v>
+        <v>9.516809262000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>8.66</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.5168092620000007</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>12</v>
+        <v>24.104012016625</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>10.40120166250001</v>
       </c>
       <c r="I29" t="n">
-        <v>500</v>
+        <v>1119.892478892</v>
       </c>
       <c r="J29" t="n">
-        <v>33.33333333333333</v>
+        <v>74.65949859279999</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2802,80 +3060,89 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="X29" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.02027777777777743</v>
+        <v>0.3863636363636369</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.001126543209876524</v>
+        <v>0.3863636363636369</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.0214646464646465</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.3863636363636369</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.0214646464646465</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.25</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>2.059069608</v>
+        <v>9.290034558</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.2900345580000003</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>24.1070332099375</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>10.70332099375001</v>
       </c>
       <c r="I30" t="n">
-        <v>500</v>
+        <v>1169.392478892</v>
       </c>
       <c r="J30" t="n">
-        <v>33.33333333333333</v>
+        <v>77.95949859279999</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2884,80 +3151,89 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="X30" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.04777777777777743</v>
+        <v>0.3636363636363642</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.002654320987654302</v>
+        <v>0.3636363636363642</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.02020202020202023</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.3636363636363642</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.02020202020202023</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.63</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>2.6640792</v>
+        <v>9.010091687999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.01009168799999927</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I31" t="n">
-        <v>500</v>
+        <v>1218.892478892</v>
       </c>
       <c r="J31" t="n">
-        <v>33.33333333333333</v>
+        <v>81.2594985928</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2966,80 +3242,89 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>-198</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="X31" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.07527777777777743</v>
+        <v>0.3409090909090915</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.004182098765432079</v>
+        <v>0.3409090909090915</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.01893939393939397</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.3409090909090915</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.01893939393939397</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>3.429473742</v>
+        <v>8.828209301999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>8.828209301999999</v>
       </c>
       <c r="G32" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I32" t="n">
-        <v>500</v>
+        <v>1267.447630053</v>
       </c>
       <c r="J32" t="n">
-        <v>33.33333333333333</v>
+        <v>84.49650867019999</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3048,80 +3333,89 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>194.220604644</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>-194.220604644</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="X32" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1027777777777774</v>
+        <v>0.3181818181818188</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.005709876543209857</v>
+        <v>0.3181818181818188</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.01767676767676771</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.3181818181818188</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.01767676767676771</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.21</v>
+        <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>3.948779808</v>
+        <v>8.488635288000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>8.488635288000001</v>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I33" t="n">
-        <v>500</v>
+        <v>1314.135124137</v>
       </c>
       <c r="J33" t="n">
-        <v>33.33333333333333</v>
+        <v>87.60900827579999</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3130,80 +3424,89 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>186.749976336</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>-186.749976336</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="X33" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1302777777777774</v>
+        <v>0.2954545454545461</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.007237654320987635</v>
+        <v>0.2954545454545461</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.01641414141414145</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.2954545454545461</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.01641414141414145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.08</v>
+        <v>8.66</v>
       </c>
       <c r="C34" t="n">
-        <v>4.585746438</v>
+        <v>8.293957799999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>8.66</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>8.293957799999999</v>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I34" t="n">
-        <v>500</v>
+        <v>1359.751892037</v>
       </c>
       <c r="J34" t="n">
-        <v>33.33333333333333</v>
+        <v>90.65012613579999</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3212,80 +3515,89 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>182.4670716</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>-182.4670716</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="X34" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1577777777777774</v>
+        <v>0.2727272727272734</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.008765432098765413</v>
+        <v>0.2727272727272734</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.01515151515151519</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.2727272727272734</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.01515151515151519</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.119999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="C35" t="n">
-        <v>5.263484598</v>
+        <v>7.991015621999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>7.991015621999999</v>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H35" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I35" t="n">
-        <v>500</v>
+        <v>1403.702477958</v>
       </c>
       <c r="J35" t="n">
-        <v>33.33333333333333</v>
+        <v>93.58016519719999</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3294,80 +3606,89 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>175.802343684</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>-175.802343684</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="X35" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1852777777777774</v>
+        <v>0.2500000000000007</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.01029320987654319</v>
+        <v>0.2500000000000007</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.01388888888888893</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.2500000000000007</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.01388888888888893</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.539999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="C36" t="n">
-        <v>5.763834048</v>
+        <v>7.540579638</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>7.540579638</v>
       </c>
       <c r="G36" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I36" t="n">
-        <v>500</v>
+        <v>1445.175665967</v>
       </c>
       <c r="J36" t="n">
-        <v>33.33333333333333</v>
+        <v>96.3450443978</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3376,80 +3697,89 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>165.892752036</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>-165.892752036</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="X36" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2127777777777774</v>
+        <v>0.2272727272727279</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.01182098765432097</v>
+        <v>0.2272727272727279</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.01262626262626266</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.2272727272727279</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.01262626262626266</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.25</v>
+        <v>7.71</v>
       </c>
       <c r="C37" t="n">
-        <v>6.085242432</v>
+        <v>7.111894061999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>7.111894061999999</v>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>24.1071383316875</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>10.71383316875001</v>
       </c>
       <c r="I37" t="n">
-        <v>500</v>
+        <v>1484.291083308</v>
       </c>
       <c r="J37" t="n">
-        <v>33.33333333333333</v>
+        <v>98.9527388872</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3458,80 +3788,89 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>156.461669364</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>-156.461669364</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="X37" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2402777777777774</v>
+        <v>0.2045454545454552</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.01334876543209875</v>
+        <v>0.2045454545454552</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.0113636363636364</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2045454545454552</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.0113636363636364</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8.65</v>
+        <v>8.92</v>
       </c>
       <c r="C38" t="n">
-        <v>6.597341838</v>
+        <v>6.46511355</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>3.608946878727272</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2.856166671272728</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>24.14473152834091</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>14.47315283409091</v>
       </c>
       <c r="I38" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J38" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3540,80 +3879,89 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>62.83566676800001</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>-62.83566676800001</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="X38" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.2677777777777774</v>
+        <v>0.1818181818181825</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.01487654320987652</v>
+        <v>0.1818181818181825</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.01010101010101014</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.1818181818181825</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.01010101010101014</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>9</v>
       </c>
       <c r="C39" t="n">
-        <v>7.112685077999999</v>
+        <v>6.164418432000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>6.164418432000001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>12</v>
+        <v>24.20894422034091</v>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>20.89442203409092</v>
       </c>
       <c r="I39" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J39" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3622,80 +3970,89 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="X39" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.2952777777777775</v>
+        <v>0.1590909090909097</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.01640432098765431</v>
+        <v>0.1590909090909097</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.008838383838383874</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.1590909090909097</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.008838383838383874</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>7.492560408</v>
+        <v>5.67882495</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>5.67882495</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>12</v>
+        <v>24.26809864690341</v>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>26.80986469034091</v>
       </c>
       <c r="I40" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J40" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3704,80 +4061,89 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="X40" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3227777777777775</v>
+        <v>0.136363636363637</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.01793209876543208</v>
+        <v>0.136363636363637</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.007575757575757611</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.136363636363637</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.007575757575757611</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>8.9</v>
       </c>
       <c r="C41" t="n">
-        <v>7.878090341999999</v>
+        <v>4.970956512</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4.970956512</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>24.31987944390341</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>31.98794439034091</v>
       </c>
       <c r="I41" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J41" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3786,80 +4152,89 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="X41" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3502777777777775</v>
+        <v>0.1136363636363643</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.01945987654320986</v>
+        <v>0.1136363636363643</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.006313131313131349</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.1136363636363643</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.006313131313131349</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.140000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="C42" t="n">
-        <v>8.338290047999999</v>
+        <v>4.457903022000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>4.457903022000001</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>24.36631593371591</v>
       </c>
       <c r="H42" t="n">
-        <v>50</v>
+        <v>36.63159337159091</v>
       </c>
       <c r="I42" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J42" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3868,80 +4243,89 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="X42" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.3777777777777775</v>
+        <v>0.09090909090909152</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.02098765432098764</v>
+        <v>0.09090909090909155</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.005050505050505086</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.09090909090909155</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.005050505050505086</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.57</v>
+        <v>8.42</v>
       </c>
       <c r="C43" t="n">
-        <v>8.478718901999999</v>
+        <v>3.797568287999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3.797568287999999</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>12</v>
+        <v>24.40587393671591</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>40.58739367159091</v>
       </c>
       <c r="I43" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J43" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3950,80 +4334,89 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="X43" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.4052777777777776</v>
+        <v>0.06818181818181879</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.02251543209876542</v>
+        <v>0.06818181818181883</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.003787878787878824</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.06818181818181883</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.003787878787878824</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8.130000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>9.141293502</v>
+        <v>3.29000595</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>3.29000595</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>12</v>
+        <v>24.44014483202841</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>44.01448320284091</v>
       </c>
       <c r="I44" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J44" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4032,80 +4425,89 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="X44" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.4327777777777776</v>
+        <v>0.04545454545454606</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0240432098765432</v>
+        <v>0.04545454545454611</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.002525252525252561</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.04545454545454611</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.002525252525252561</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>8.978487462</v>
+        <v>2.612099328</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2.612099328</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>12</v>
+        <v>24.46735420002841</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>46.73542000284091</v>
       </c>
       <c r="I45" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J45" t="n">
-        <v>33.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4114,80 +4516,89 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="X45" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.4602777777777776</v>
+        <v>0.02272727272727333</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.02557098765432098</v>
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.001262626262626299</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.000548902</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-6.999451098</v>
+      </c>
+      <c r="F46" t="n">
         <v>9</v>
       </c>
-      <c r="C46" t="n">
-        <v>9.541429398</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
       <c r="G46" t="n">
-        <v>12</v>
+        <v>24.39444325109091</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>39.44432510909091</v>
       </c>
       <c r="I46" t="n">
-        <v>500</v>
+        <v>499.9999999999995</v>
       </c>
       <c r="J46" t="n">
-        <v>33.33333333333333</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4196,13 +4607,13 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>4000</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>4198</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -4229,47 +4640,56 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.4877777777777776</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.02709876543209876</v>
+        <v>0.3343181818181827</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.01857323232323237</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.358764782</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-7.641235218</v>
+      </c>
+      <c r="F47" t="n">
         <v>9</v>
       </c>
-      <c r="C47" t="n">
-        <v>9.711852552</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>24.31484705090341</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>31.48470509034091</v>
       </c>
       <c r="I47" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4278,13 +4698,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>1999.999999999998</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>2197.999999999998</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -4311,47 +4731,56 @@
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.5152777777777776</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.02862654320987654</v>
+        <v>0.6395959595959603</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.03553310886644224</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6906375119999999</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-8.309362488</v>
+      </c>
+      <c r="F48" t="n">
         <v>9</v>
       </c>
-      <c r="C48" t="n">
-        <v>9.5629002</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>24.22829119165341</v>
       </c>
       <c r="H48" t="n">
-        <v>50</v>
+        <v>22.82911916534091</v>
       </c>
       <c r="I48" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4360,13 +4789,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -4393,47 +4822,56 @@
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.5427777777777776</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.03015432098765431</v>
+        <v>0.6670959595959602</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.03706088664422001</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.65</v>
+        <v>7.34</v>
       </c>
       <c r="C49" t="n">
-        <v>10.026753192</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>24.13454119165341</v>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>13.45411916534091</v>
       </c>
       <c r="I49" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4442,13 +4880,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -4475,47 +4913,56 @@
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.5702777777777776</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.03168209876543208</v>
+        <v>0.6945959595959602</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.03858866442199779</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.59</v>
+        <v>6.5</v>
       </c>
       <c r="C50" t="n">
-        <v>10.000384128</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>24.04079119165341</v>
       </c>
       <c r="H50" t="n">
-        <v>50</v>
+        <v>4.079119165340911</v>
       </c>
       <c r="I50" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4524,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -4557,47 +5004,56 @@
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.5977777777777775</v>
+        <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.03320987654320987</v>
+        <v>0.7220959595959602</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.04011644219977557</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>11.37404560127273</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-3.915954398727274</v>
+      </c>
+      <c r="F51" t="n">
         <v>9</v>
       </c>
-      <c r="C51" t="n">
-        <v>9.902930568000002</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4606,13 +5062,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -4639,47 +5095,56 @@
         <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.6252777777777775</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.03473765432098764</v>
+        <v>0.7495959595959601</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.04164421997755334</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.039999999999999</v>
+        <v>5.72</v>
       </c>
       <c r="C52" t="n">
-        <v>9.910027782</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>14.72</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G52" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4688,13 +5153,13 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4721,47 +5186,56 @@
         <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.6527777777777775</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.03626543209876542</v>
+        <v>0.7770959595959601</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.04317199775533112</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8.49</v>
+        <v>5.13</v>
       </c>
       <c r="C53" t="n">
-        <v>10.134611022</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>14.13</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4770,13 +5244,13 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4803,47 +5277,56 @@
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.6802777777777774</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.03779320987654319</v>
+        <v>0.8045959595959601</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.04469977553310889</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
         <v>9</v>
       </c>
-      <c r="C54" t="n">
-        <v>9.893447928000001</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
       <c r="G54" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4852,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4885,47 +5368,56 @@
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.7077777777777774</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.03932098765432097</v>
+        <v>0.8320959595959601</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.04622755331088667</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8.609999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="C55" t="n">
-        <v>9.932678861999999</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>13.85</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -4934,13 +5426,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4967,47 +5459,56 @@
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.7352777777777774</v>
+        <v>1</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.04084876543209874</v>
+        <v>0.85959595959596</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.04775533108866445</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8.57</v>
+        <v>5.4</v>
       </c>
       <c r="C56" t="n">
-        <v>9.7100352</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -5016,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -5049,47 +5550,56 @@
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.7627777777777773</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.04237654320987652</v>
+        <v>0.88709595959596</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.04928310886644223</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>8.66</v>
+        <v>4.78</v>
       </c>
       <c r="C57" t="n">
-        <v>9.516809262000001</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>13.78</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -5098,13 +5608,13 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -5131,47 +5641,56 @@
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.7902777777777773</v>
+        <v>1</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.0439043209876543</v>
+        <v>0.91459595959596</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.05081088664422</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.539999999999999</v>
+        <v>4.06</v>
       </c>
       <c r="C58" t="n">
-        <v>9.290034558</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>13.06</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5180,13 +5699,13 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
@@ -5213,47 +5732,56 @@
         <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.8177777777777773</v>
+        <v>1</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.04543209876543207</v>
+        <v>0.9420959595959599</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.05233866442199778</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
         <v>9</v>
       </c>
-      <c r="C59" t="n">
-        <v>9.010091687999999</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -5262,13 +5790,13 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
@@ -5295,47 +5823,56 @@
         <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.8452777777777772</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.04695987654320984</v>
+        <v>0.9695959595959599</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.05386644219977555</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
         <v>9</v>
       </c>
-      <c r="C60" t="n">
-        <v>8.828209301999999</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
       <c r="G60" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5344,13 +5881,13 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
@@ -5377,47 +5914,56 @@
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>0.05555555555555555</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.8727777777777772</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.04848765432098762</v>
+        <v>0.9970959595959599</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.05539421997755332</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.02272727272727338</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.001262626262626299</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
         <v>9</v>
       </c>
-      <c r="C61" t="n">
-        <v>8.488635288000001</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
       <c r="G61" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5426,13 +5972,13 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
@@ -5459,47 +6005,56 @@
         <v>1</v>
       </c>
       <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y61" t="n">
-        <v>0.9002777777777772</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0.0500154320987654</v>
+      <c r="AB61" t="n">
+        <v>0.04732323232323325</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.002629068462401847</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8.66</v>
+        <v>3.5</v>
       </c>
       <c r="C62" t="n">
-        <v>8.293957799999999</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -5508,13 +6063,13 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -5541,47 +6096,56 @@
         <v>1</v>
       </c>
       <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y62" t="n">
-        <v>0.9277777777777771</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0.05154320987654317</v>
+      <c r="AB62" t="n">
+        <v>0.07482323232323325</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.004156846240179625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8.92</v>
+        <v>2.79</v>
       </c>
       <c r="C63" t="n">
-        <v>7.991015621999999</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>11.79</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5590,13 +6154,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P63" t="n">
         <v>1</v>
@@ -5623,47 +6187,56 @@
         <v>1</v>
       </c>
       <c r="X63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y63" t="n">
-        <v>0.9552777777777771</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0.05307098765432095</v>
+      <c r="AB63" t="n">
+        <v>0.1023232323232332</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0.005684624017957403</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8.42</v>
+        <v>3.15</v>
       </c>
       <c r="C64" t="n">
-        <v>7.540579638</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>12.15</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5672,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
@@ -5705,47 +6278,56 @@
         <v>1</v>
       </c>
       <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y64" t="n">
-        <v>0.9827777777777771</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0.05459876543209873</v>
+      <c r="AB64" t="n">
+        <v>0.1298232323232333</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0.007212401795735181</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7.71</v>
+        <v>2.31</v>
       </c>
       <c r="C65" t="n">
-        <v>7.111894061999999</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5754,13 +6336,13 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -5787,47 +6369,56 @@
         <v>1</v>
       </c>
       <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA65" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB65" t="n">
+        <v>0.1573232323232333</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0.008740179573512958</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8.92</v>
+        <v>2.8</v>
       </c>
       <c r="C66" t="n">
-        <v>6.46511355</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5836,13 +6427,13 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5869,47 +6460,56 @@
         <v>1</v>
       </c>
       <c r="X66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA66" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB66" t="n">
+        <v>0.1848232323232332</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.01026795735129074</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="B67" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
         <v>9</v>
       </c>
-      <c r="C67" t="n">
-        <v>6.164418432000001</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
       <c r="G67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5918,13 +6518,13 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
@@ -5951,47 +6551,56 @@
         <v>1</v>
       </c>
       <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA67" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB67" t="n">
+        <v>0.2123232323232332</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.01179573512906851</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
         <v>9</v>
       </c>
-      <c r="C68" t="n">
-        <v>5.67882495</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
       <c r="G68" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -6000,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -6033,47 +6642,56 @@
         <v>1</v>
       </c>
       <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB68" t="n">
+        <v>0.2398232323232332</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.01332351290684629</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8.9</v>
+        <v>3.11</v>
       </c>
       <c r="C69" t="n">
-        <v>4.970956512</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>12.11</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H69" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6082,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -6115,47 +6733,56 @@
         <v>1</v>
       </c>
       <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA69" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB69" t="n">
+        <v>0.2673232323232332</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.01485129068462407</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8.25</v>
+        <v>2.33</v>
       </c>
       <c r="C70" t="n">
-        <v>4.457903022000001</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>11.33</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G70" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6164,13 +6791,13 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -6197,47 +6824,56 @@
         <v>1</v>
       </c>
       <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA70" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB70" t="n">
+        <v>0.2948232323232333</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.01637906846240185</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>8.42</v>
+        <v>3.1</v>
       </c>
       <c r="C71" t="n">
-        <v>3.797568287999999</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6246,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -6279,47 +6915,56 @@
         <v>1</v>
       </c>
       <c r="X71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA71" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB71" t="n">
+        <v>0.3223232323232333</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.01790684624017963</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8.369999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="C72" t="n">
-        <v>3.29000595</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>11.84</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -6328,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
@@ -6361,47 +7006,56 @@
         <v>1</v>
       </c>
       <c r="X72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA72" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB72" t="n">
+        <v>0.3498232323232333</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.01943462401795741</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8.039999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="C73" t="n">
-        <v>2.612099328</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6410,13 +7064,13 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P73" t="n">
         <v>1</v>
@@ -6443,47 +7097,56 @@
         <v>1</v>
       </c>
       <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA73" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB73" t="n">
+        <v>0.3773232323232333</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.02096240179573518</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.31</v>
+        <v>2.52</v>
       </c>
       <c r="C74" t="n">
-        <v>2.000548902</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>11.52</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -6492,13 +7155,13 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -6525,47 +7188,56 @@
         <v>1</v>
       </c>
       <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA74" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y74" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB74" t="n">
+        <v>0.4048232323232334</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.02249017957351297</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7.17</v>
+        <v>3.34</v>
       </c>
       <c r="C75" t="n">
-        <v>1.358764782</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H75" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -6574,13 +7246,13 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -6607,47 +7279,56 @@
         <v>1</v>
       </c>
       <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA75" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y75" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB75" t="n">
+        <v>0.4323232323232334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.02401795735129075</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6.48</v>
+        <v>2.31</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6906375119999999</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G76" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6656,13 +7337,13 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P76" t="n">
         <v>1</v>
@@ -6689,47 +7370,56 @@
         <v>1</v>
       </c>
       <c r="X76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA76" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB76" t="n">
+        <v>0.4598232323232334</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.02554573512906852</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>7.34</v>
+        <v>2.57</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>11.57</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6738,13 +7428,13 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -6771,47 +7461,56 @@
         <v>1</v>
       </c>
       <c r="X77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA77" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB77" t="n">
+        <v>0.4873232323232334</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.0270735129068463</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H78" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6820,13 +7519,13 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -6853,47 +7552,56 @@
         <v>1</v>
       </c>
       <c r="X78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB78" t="n">
+        <v>0.5148232323232335</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.02860129068462408</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6.29</v>
+        <v>2.41</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>11.41</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H79" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6902,13 +7610,13 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
@@ -6935,47 +7643,56 @@
         <v>1</v>
       </c>
       <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB79" t="n">
+        <v>0.5423232323232334</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.03012906846240185</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5.72</v>
+        <v>2.48</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>11.48</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G80" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H80" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -6984,13 +7701,13 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -7017,47 +7734,56 @@
         <v>1</v>
       </c>
       <c r="X80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB80" t="n">
+        <v>0.5698232323232334</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.03165684624017963</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5.13</v>
+        <v>2.7</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H81" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -7066,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
@@ -7099,47 +7825,56 @@
         <v>1</v>
       </c>
       <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA81" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB81" t="n">
+        <v>0.5973232323232334</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0.03318462401795741</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5.87</v>
+        <v>3.28</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>12.28</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H82" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -7148,13 +7883,13 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P82" t="n">
         <v>1</v>
@@ -7181,47 +7916,56 @@
         <v>1</v>
       </c>
       <c r="X82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA82" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB82" t="n">
+        <v>0.6248232323232333</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0.03471240179573518</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G83" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H83" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7230,13 +7974,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -7263,47 +8007,56 @@
         <v>1</v>
       </c>
       <c r="X83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA83" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB83" t="n">
+        <v>0.6523232323232333</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0.03624017957351296</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5.4</v>
+        <v>2.57</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>11.57</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H84" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -7312,13 +8065,13 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
@@ -7345,47 +8098,56 @@
         <v>1</v>
       </c>
       <c r="X84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA84" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB84" t="n">
+        <v>0.6798232323232333</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0.03776795735129074</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4.78</v>
+        <v>2.57</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>11.57</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -7394,13 +8156,13 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -7427,47 +8189,56 @@
         <v>1</v>
       </c>
       <c r="X85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB85" t="n">
+        <v>0.7073232323232332</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.03929573512906851</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.06</v>
+        <v>3.54</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>12.54</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G86" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H86" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7476,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -7509,47 +8280,56 @@
         <v>1</v>
       </c>
       <c r="X86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA86" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB86" t="n">
+        <v>0.7348232323232332</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0.04082351290684629</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>12.54</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -7558,13 +8338,13 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -7591,47 +8371,56 @@
         <v>1</v>
       </c>
       <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA87" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB87" t="n">
+        <v>0.7623232323232332</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.04235129068462407</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G88" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H88" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7640,13 +8429,13 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P88" t="n">
         <v>1</v>
@@ -7673,47 +8462,56 @@
         <v>1</v>
       </c>
       <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB88" t="n">
+        <v>0.7898232323232331</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0.04387906846240185</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>11.87</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G89" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7722,13 +8520,13 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -7755,47 +8553,56 @@
         <v>1</v>
       </c>
       <c r="X89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB89" t="n">
+        <v>0.8173232323232331</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0.04540684624017962</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H90" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -7804,13 +8611,13 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P90" t="n">
         <v>1</v>
@@ -7837,47 +8644,56 @@
         <v>1</v>
       </c>
       <c r="X90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB90" t="n">
+        <v>0.8448232323232331</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0.04693462401795739</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>12.28</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G91" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H91" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -7886,13 +8702,13 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P91" t="n">
         <v>1</v>
@@ -7919,47 +8735,56 @@
         <v>1</v>
       </c>
       <c r="X91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB91" t="n">
+        <v>0.8723232323232331</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0.04846240179573517</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>11.39</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G92" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H92" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7968,13 +8793,13 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -8001,47 +8826,56 @@
         <v>1</v>
       </c>
       <c r="X92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y92" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB92" t="n">
+        <v>0.899823232323233</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.04999017957351295</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.31</v>
+        <v>3.16</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>12.16</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G93" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H93" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8050,13 +8884,13 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -8083,47 +8917,56 @@
         <v>1</v>
       </c>
       <c r="X93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB93" t="n">
+        <v>0.927323232323233</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0.05151795735129072</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>11.31</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G94" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8132,13 +8975,13 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
@@ -8165,47 +9008,56 @@
         <v>1</v>
       </c>
       <c r="X94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA94" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB94" t="n">
+        <v>0.954823232323233</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0.0530457351290685</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>12.14</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G95" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8214,13 +9066,13 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -8247,47 +9099,56 @@
         <v>1</v>
       </c>
       <c r="X95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA95" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y95" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>0.05555555555555555</v>
+      <c r="AB95" t="n">
+        <v>0.9823232323232329</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0.05457351290684627</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.61</v>
+        <v>4.35</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.6889206480000001</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>9.446203318941951</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>5.78512396694195</v>
       </c>
       <c r="G96" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -8296,13 +9157,13 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>127.2727272727229</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>127.2727272727229</v>
       </c>
       <c r="P96" t="n">
         <v>1</v>
@@ -8329,47 +9190,56 @@
         <v>1</v>
       </c>
       <c r="X96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA96" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z96" t="n">
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3.11</v>
+        <v>4.14</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1.402933752</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1.402933752</v>
       </c>
       <c r="G97" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H97" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>500</v>
+        <v>7.716135635999999</v>
       </c>
       <c r="J97" t="n">
-        <v>33.33333333333333</v>
+        <v>0.5144090424</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -8378,13 +9248,13 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>30.864542544</v>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>-30.864542544</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
@@ -8411,12 +9281,21 @@
         <v>1</v>
       </c>
       <c r="X97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA97" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="Y97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" t="n">
+      <c r="AB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>

--- a/risultati_dettagliati_microgrid.xlsx
+++ b/risultati_dettagliati_microgrid.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AA97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,30 +534,20 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>CargoBike_5_SOC_kg</t>
+          <t>Forklift_1_SOC_kg</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>CargoBike_5_SOC_Percent</t>
+          <t>Forklift_1_SOC_Percent</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Forklift_1_SOC_kg</t>
+          <t>Forklift_2_SOC_kg</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
-        <is>
-          <t>Forklift_1_SOC_Percent</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Forklift_2_SOC_kg</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
         <is>
           <t>Forklift_2_SOC_Percent</t>
         </is>
@@ -570,31 +560,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.059069608</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.059069608</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>11.324882844</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.7549921896000001</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -603,10 +593,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>45.299531376</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-45.299531376</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -639,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
@@ -647,12 +637,6 @@
       <c r="AA2" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.05555555555555555</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,13 +645,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.63</v>
+        <v>1.5</v>
       </c>
       <c r="C3" t="n">
         <v>2.6640792</v>
       </c>
       <c r="D3" t="n">
-        <v>5.63</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -682,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>14.6524356</v>
+        <v>25.977318444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.97682904</v>
+        <v>1.7318212296</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -703,46 +687,40 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.05416666666666666</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.975</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0542929292929293</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.9772727272727273</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0542929292929293</v>
+        <v>0.05416666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -752,13 +730,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5</v>
+        <v>1.59</v>
       </c>
       <c r="C4" t="n">
         <v>3.429473742</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>1.59</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -773,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>33.514541181</v>
+        <v>44.839424025</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2343027454</v>
+        <v>2.989294935</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -794,46 +772,40 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.05277777777777777</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05303030303030304</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.9545454545454546</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.05303030303030304</v>
+        <v>0.05277777777777777</v>
       </c>
     </row>
     <row r="5">
@@ -843,13 +815,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.21</v>
+        <v>1.47</v>
       </c>
       <c r="C5" t="n">
         <v>3.948779808</v>
       </c>
       <c r="D5" t="n">
-        <v>6.21</v>
+        <v>1.47</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -864,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>55.23283012499999</v>
+        <v>66.55771296899999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.682188675</v>
+        <v>4.437180864599999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -885,46 +857,40 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.05138888888888888</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9318181818181819</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05176767676767677</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.9318181818181819</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.05176767676767677</v>
+        <v>0.05138888888888888</v>
       </c>
     </row>
     <row r="6">
@@ -934,13 +900,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.08</v>
+        <v>1.55</v>
       </c>
       <c r="C6" t="n">
         <v>4.585746438</v>
       </c>
       <c r="D6" t="n">
-        <v>8.08</v>
+        <v>1.55</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -955,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>80.454435534</v>
+        <v>91.779318378</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3636290356</v>
+        <v>6.1186212252</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -976,46 +942,40 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0505050505050505</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.9090909090909092</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0505050505050505</v>
+        <v>0.04999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1025,13 +985,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.119999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="C7" t="n">
         <v>5.263484598</v>
       </c>
       <c r="D7" t="n">
-        <v>8.119999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1046,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>109.403600823</v>
+        <v>120.728483667</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2935733882</v>
+        <v>8.0485655778</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,46 +1027,40 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.0486111111111111</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8863636363636365</v>
+        <v>0.8749999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.04924242424242425</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.8863636363636365</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.04924242424242425</v>
+        <v>0.0486111111111111</v>
       </c>
     </row>
     <row r="8">
@@ -1116,13 +1070,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.539999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="C8" t="n">
         <v>5.763834048</v>
       </c>
       <c r="D8" t="n">
-        <v>8.539999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1137,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>141.104688087</v>
+        <v>152.429570931</v>
       </c>
       <c r="J8" t="n">
-        <v>9.406979205799999</v>
+        <v>10.1619713954</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1158,46 +1112,40 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8636363636363639</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8636363636363639</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8636363636363639</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8636363636363639</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8636363636363639</v>
+        <v>0.04722222222222221</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.04797979797979798</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.8636363636363638</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.04797979797979798</v>
+        <v>0.04722222222222221</v>
       </c>
     </row>
     <row r="9">
@@ -1207,13 +1155,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.25</v>
+        <v>1.48</v>
       </c>
       <c r="C9" t="n">
         <v>6.085242432</v>
       </c>
       <c r="D9" t="n">
-        <v>8.25</v>
+        <v>1.48</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1228,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>174.573521463</v>
+        <v>185.898404307</v>
       </c>
       <c r="J9" t="n">
-        <v>11.6382347642</v>
+        <v>12.3932269538</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1249,46 +1197,40 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8409090909090912</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8409090909090912</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8409090909090912</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8409090909090912</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="X9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8409090909090912</v>
+        <v>0.04583333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8409090909090911</v>
+        <v>0.8249999999999998</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04671717171717173</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.8409090909090911</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.04671717171717173</v>
+        <v>0.04583333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1298,13 +1240,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.65</v>
+        <v>1.42</v>
       </c>
       <c r="C10" t="n">
         <v>6.597341838</v>
       </c>
       <c r="D10" t="n">
-        <v>8.65</v>
+        <v>1.42</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1319,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>210.858901572</v>
+        <v>222.183784416</v>
       </c>
       <c r="J10" t="n">
-        <v>14.0572601048</v>
+        <v>14.8122522944</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1340,46 +1282,40 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8181818181818185</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8181818181818185</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8181818181818185</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8181818181818185</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8181818181818185</v>
+        <v>0.04444444444444444</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.8181818181818183</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.8181818181818183</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04444444444444444</v>
       </c>
     </row>
     <row r="11">
@@ -1389,13 +1325,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>1.32</v>
       </c>
       <c r="C11" t="n">
         <v>7.112685077999999</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>1.32</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1410,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>249.978669501</v>
+        <v>261.303552345</v>
       </c>
       <c r="J11" t="n">
-        <v>16.6652446334</v>
+        <v>17.420236823</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1431,46 +1367,40 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7954545454545457</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7954545454545457</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7954545454545457</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7954545454545457</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7954545454545457</v>
+        <v>0.04305555555555554</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7954545454545456</v>
+        <v>0.7749999999999998</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0441919191919192</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.7954545454545456</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.0441919191919192</v>
+        <v>0.04305555555555554</v>
       </c>
     </row>
     <row r="12">
@@ -1480,13 +1410,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="C12" t="n">
         <v>7.492560408</v>
       </c>
       <c r="D12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1501,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>291.187751745</v>
+        <v>302.512634589</v>
       </c>
       <c r="J12" t="n">
-        <v>19.412516783</v>
+        <v>20.1675089726</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1522,46 +1452,40 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.04166666666666665</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.7727272727272729</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04292929292929294</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.7727272727272729</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.04292929292929294</v>
+        <v>0.04166666666666665</v>
       </c>
     </row>
     <row r="13">
@@ -1571,13 +1495,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.9</v>
+        <v>1.21</v>
       </c>
       <c r="C13" t="n">
         <v>7.878090341999999</v>
       </c>
       <c r="D13" t="n">
-        <v>8.9</v>
+        <v>1.21</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1592,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>334.517248626</v>
+        <v>345.84213147</v>
       </c>
       <c r="J13" t="n">
-        <v>22.3011499084</v>
+        <v>23.056142098</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1613,46 +1537,40 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.04027777777777776</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.7249999999999998</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04166666666666668</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.7500000000000002</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.04166666666666668</v>
+        <v>0.04027777777777776</v>
       </c>
     </row>
     <row r="14">
@@ -1662,13 +1580,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.140000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="C14" t="n">
         <v>8.338290047999999</v>
       </c>
       <c r="D14" t="n">
-        <v>8.140000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1683,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>380.37784389</v>
+        <v>391.702726734</v>
       </c>
       <c r="J14" t="n">
-        <v>25.358522926</v>
+        <v>26.11351511559999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1704,46 +1622,40 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.03888888888888888</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.7272727272727275</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.04040404040404041</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.7272727272727275</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.03888888888888888</v>
       </c>
     </row>
     <row r="15">
@@ -1753,13 +1665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.57</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>8.478718901999999</v>
       </c>
       <c r="D15" t="n">
-        <v>7.57</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1774,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>427.010797851</v>
+        <v>438.335680695</v>
       </c>
       <c r="J15" t="n">
-        <v>28.4673865234</v>
+        <v>29.222378713</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1795,46 +1707,40 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.03749999999999998</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7045454545454548</v>
+        <v>0.6749999999999997</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03914141414141416</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.7045454545454548</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.03914141414141416</v>
+        <v>0.03749999999999998</v>
       </c>
     </row>
     <row r="16">
@@ -1844,13 +1750,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.130000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="C16" t="n">
         <v>9.141293502</v>
       </c>
       <c r="D16" t="n">
-        <v>8.130000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="E16" t="n">
         <v>0.1412935019999999</v>
@@ -1865,10 +1771,10 @@
         <v>0.1471807312499999</v>
       </c>
       <c r="I16" t="n">
-        <v>476.510797851</v>
+        <v>487.835680695</v>
       </c>
       <c r="J16" t="n">
-        <v>31.7673865234</v>
+        <v>32.52237871299999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1886,46 +1792,40 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.03611111111111109</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.6818181818181821</v>
+        <v>0.6499999999999997</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.03787878787878789</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.6818181818181821</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.03787878787878789</v>
+        <v>0.03611111111111109</v>
       </c>
     </row>
     <row r="17">
@@ -1935,13 +1835,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="C17" t="n">
         <v>8.978487462</v>
       </c>
       <c r="D17" t="n">
-        <v>8.800000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1956,10 +1856,10 @@
         <v>0.1471807312499999</v>
       </c>
       <c r="I17" t="n">
-        <v>525.892478892</v>
+        <v>537.2173617359999</v>
       </c>
       <c r="J17" t="n">
-        <v>35.0594985928</v>
+        <v>35.81449078239999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1977,46 +1877,40 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.0347222222222222</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.6590909090909094</v>
+        <v>0.6249999999999997</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.03661616161616164</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.6590909090909094</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.03661616161616164</v>
+        <v>0.0347222222222222</v>
       </c>
     </row>
     <row r="18">
@@ -2026,13 +1920,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>1.42</v>
       </c>
       <c r="C18" t="n">
         <v>9.541429398</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>1.42</v>
       </c>
       <c r="E18" t="n">
         <v>0.541429398</v>
@@ -2047,10 +1941,10 @@
         <v>0.7111696875</v>
       </c>
       <c r="I18" t="n">
-        <v>575.392478892</v>
+        <v>586.7173617359999</v>
       </c>
       <c r="J18" t="n">
-        <v>38.3594985928</v>
+        <v>39.1144907824</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2068,46 +1962,40 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.03333333333333332</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.6363636363636367</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.03535353535353537</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.6363636363636367</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.03535353535353537</v>
+        <v>0.03333333333333332</v>
       </c>
     </row>
     <row r="19">
@@ -2117,13 +2005,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>1.24</v>
       </c>
       <c r="C19" t="n">
         <v>9.711852552</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>1.24</v>
       </c>
       <c r="E19" t="n">
         <v>0.7118525519999999</v>
@@ -2138,10 +2026,10 @@
         <v>1.4526827625</v>
       </c>
       <c r="I19" t="n">
-        <v>624.892478892</v>
+        <v>636.2173617359999</v>
       </c>
       <c r="J19" t="n">
-        <v>41.6594985928</v>
+        <v>42.41449078239999</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2159,46 +2047,40 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="R19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="S19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="T19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="U19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="V19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="W19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="X19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.03194444444444443</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.613636363636364</v>
+        <v>0.5749999999999996</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.03409090909090911</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.613636363636364</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.03409090909090911</v>
+        <v>0.03194444444444443</v>
       </c>
     </row>
     <row r="20">
@@ -2208,13 +2090,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="C20" t="n">
         <v>9.5629002</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0.5629001999999996</v>
@@ -2229,10 +2111,10 @@
         <v>2.039037137499999</v>
       </c>
       <c r="I20" t="n">
-        <v>674.392478892</v>
+        <v>685.7173617359999</v>
       </c>
       <c r="J20" t="n">
-        <v>44.9594985928</v>
+        <v>45.7144907824</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2250,46 +2132,40 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.03055555555555553</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.5909090909090913</v>
+        <v>0.5499999999999996</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.03282828282828285</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.5909090909090913</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.03282828282828285</v>
+        <v>0.03055555555555553</v>
       </c>
     </row>
     <row r="21">
@@ -2299,13 +2175,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.65</v>
+        <v>1.36</v>
       </c>
       <c r="C21" t="n">
         <v>10.026753192</v>
       </c>
       <c r="D21" t="n">
-        <v>8.65</v>
+        <v>1.36</v>
       </c>
       <c r="E21" t="n">
         <v>1.026753192000001</v>
@@ -2320,10 +2196,10 @@
         <v>3.1085717125</v>
       </c>
       <c r="I21" t="n">
-        <v>723.892478892</v>
+        <v>735.2173617359999</v>
       </c>
       <c r="J21" t="n">
-        <v>48.2594985928</v>
+        <v>49.0144907824</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2341,46 +2217,40 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.02916666666666664</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5681818181818186</v>
+        <v>0.5249999999999996</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.03156565656565658</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.5681818181818186</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.03156565656565658</v>
+        <v>0.02916666666666664</v>
       </c>
     </row>
     <row r="22">
@@ -2390,13 +2260,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.59</v>
+        <v>1.55</v>
       </c>
       <c r="C22" t="n">
         <v>10.000384128</v>
       </c>
       <c r="D22" t="n">
-        <v>8.59</v>
+        <v>1.55</v>
       </c>
       <c r="E22" t="n">
         <v>1.000384128000002</v>
@@ -2411,10 +2281,10 @@
         <v>4.150638512500002</v>
       </c>
       <c r="I22" t="n">
-        <v>773.392478892</v>
+        <v>784.7173617359999</v>
       </c>
       <c r="J22" t="n">
-        <v>51.5594985928</v>
+        <v>52.31449078239999</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2432,46 +2302,40 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.02777777777777775</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.5454545454545459</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.03030303030303032</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.5454545454545459</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.03030303030303032</v>
+        <v>0.02777777777777775</v>
       </c>
     </row>
     <row r="23">
@@ -2481,13 +2345,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>1.58</v>
       </c>
       <c r="C23" t="n">
         <v>9.902930568000002</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>1.58</v>
       </c>
       <c r="E23" t="n">
         <v>0.9029305680000022</v>
@@ -2502,10 +2366,10 @@
         <v>5.091191187500005</v>
       </c>
       <c r="I23" t="n">
-        <v>822.892478892</v>
+        <v>834.2173617359999</v>
       </c>
       <c r="J23" t="n">
-        <v>54.8594985928</v>
+        <v>55.6144907824</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2523,46 +2387,40 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.02638888888888886</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.5227272727272732</v>
+        <v>0.4749999999999995</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02904040404040406</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.5227272727272732</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.02904040404040406</v>
+        <v>0.02638888888888886</v>
       </c>
     </row>
     <row r="24">
@@ -2572,13 +2430,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8.039999999999999</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>9.910027782</v>
       </c>
       <c r="D24" t="n">
-        <v>8.039999999999999</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0.9100277820000002</v>
@@ -2593,10 +2451,10 @@
         <v>6.039136793750005</v>
       </c>
       <c r="I24" t="n">
-        <v>872.392478892</v>
+        <v>883.7173617359999</v>
       </c>
       <c r="J24" t="n">
-        <v>58.1594985928</v>
+        <v>58.91449078239999</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2614,46 +2472,40 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="X24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.02499999999999997</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.4499999999999995</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0277777777777778</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.5000000000000004</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.0277777777777778</v>
+        <v>0.02499999999999997</v>
       </c>
     </row>
     <row r="25">
@@ -2663,13 +2515,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.49</v>
+        <v>1.41</v>
       </c>
       <c r="C25" t="n">
         <v>10.134611022</v>
       </c>
       <c r="D25" t="n">
-        <v>8.49</v>
+        <v>1.41</v>
       </c>
       <c r="E25" t="n">
         <v>1.134611022</v>
@@ -2684,10 +2536,10 @@
         <v>7.221023275000005</v>
       </c>
       <c r="I25" t="n">
-        <v>921.892478892</v>
+        <v>933.2173617359999</v>
       </c>
       <c r="J25" t="n">
-        <v>61.4594985928</v>
+        <v>62.2144907824</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2705,46 +2557,40 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="W25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="X25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.02361111111111108</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4772727272727277</v>
+        <v>0.4249999999999995</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.02651515151515154</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.4772727272727277</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.02651515151515154</v>
+        <v>0.02361111111111108</v>
       </c>
     </row>
     <row r="26">
@@ -2754,13 +2600,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>1.46</v>
       </c>
       <c r="C26" t="n">
         <v>9.893447928000001</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>1.46</v>
       </c>
       <c r="E26" t="n">
         <v>0.8934479280000005</v>
@@ -2775,10 +2621,10 @@
         <v>8.151698200000006</v>
       </c>
       <c r="I26" t="n">
-        <v>971.392478892</v>
+        <v>982.7173617359999</v>
       </c>
       <c r="J26" t="n">
-        <v>64.7594985928</v>
+        <v>65.51449078239999</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2796,46 +2642,40 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="R26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="S26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="T26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="U26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="V26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="W26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="X26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.02222222222222219</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.454545454545455</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.02525252525252528</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.454545454545455</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.02525252525252528</v>
+        <v>0.02222222222222219</v>
       </c>
     </row>
     <row r="27">
@@ -2845,13 +2685,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.609999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="C27" t="n">
         <v>9.932678861999999</v>
       </c>
       <c r="D27" t="n">
-        <v>8.609999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="E27" t="n">
         <v>0.9326788619999995</v>
@@ -2866,10 +2706,10 @@
         <v>9.123238681250005</v>
       </c>
       <c r="I27" t="n">
-        <v>1020.892478892</v>
+        <v>1032.217361736</v>
       </c>
       <c r="J27" t="n">
-        <v>68.0594985928</v>
+        <v>68.8144907824</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2887,46 +2727,40 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="W27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="X27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.4318181818181823</v>
+        <v>0.3749999999999994</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.02398989898989902</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.4318181818181823</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.02398989898989902</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -2936,13 +2770,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.57</v>
+        <v>1.42</v>
       </c>
       <c r="C28" t="n">
         <v>9.7100352</v>
       </c>
       <c r="D28" t="n">
-        <v>8.57</v>
+        <v>1.42</v>
       </c>
       <c r="E28" t="n">
         <v>0.7100352000000001</v>
@@ -2957,10 +2791,10 @@
         <v>9.862858681250005</v>
       </c>
       <c r="I28" t="n">
-        <v>1070.392478892</v>
+        <v>1081.717361736</v>
       </c>
       <c r="J28" t="n">
-        <v>71.35949859279999</v>
+        <v>72.1144907824</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2978,46 +2812,40 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="R28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="V28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.01944444444444441</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.4090909090909096</v>
+        <v>0.3499999999999994</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.02272727272727276</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0.4090909090909096</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0.02272727272727276</v>
+        <v>0.01944444444444441</v>
       </c>
     </row>
     <row r="29">
@@ -3027,13 +2855,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8.66</v>
+        <v>1.37</v>
       </c>
       <c r="C29" t="n">
         <v>9.516809262000001</v>
       </c>
       <c r="D29" t="n">
-        <v>8.66</v>
+        <v>1.37</v>
       </c>
       <c r="E29" t="n">
         <v>0.5168092620000007</v>
@@ -3048,10 +2876,10 @@
         <v>10.40120166250001</v>
       </c>
       <c r="I29" t="n">
-        <v>1119.892478892</v>
+        <v>1131.217361736</v>
       </c>
       <c r="J29" t="n">
-        <v>74.65949859279999</v>
+        <v>75.41449078239999</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3069,46 +2897,40 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="V29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="W29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="X29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.01805555555555552</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3863636363636369</v>
+        <v>0.3249999999999994</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0214646464646465</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.3863636363636369</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.0214646464646465</v>
+        <v>0.01805555555555552</v>
       </c>
     </row>
     <row r="30">
@@ -3118,13 +2940,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8.539999999999999</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
         <v>9.290034558</v>
       </c>
       <c r="D30" t="n">
-        <v>8.539999999999999</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>0.2900345580000003</v>
@@ -3139,10 +2961,10 @@
         <v>10.70332099375001</v>
       </c>
       <c r="I30" t="n">
-        <v>1169.392478892</v>
+        <v>1180.717361736</v>
       </c>
       <c r="J30" t="n">
-        <v>77.95949859279999</v>
+        <v>78.71449078239999</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3160,46 +2982,40 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="W30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.01666666666666663</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3636363636363642</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02020202020202023</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0.3636363636363642</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.02020202020202023</v>
+        <v>0.01666666666666663</v>
       </c>
     </row>
     <row r="31">
@@ -3209,13 +3025,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>6.16</v>
       </c>
       <c r="C31" t="n">
         <v>9.010091687999999</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>6.16</v>
       </c>
       <c r="E31" t="n">
         <v>0.01009168799999927</v>
@@ -3230,10 +3046,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I31" t="n">
-        <v>1218.892478892</v>
+        <v>1230.217361736</v>
       </c>
       <c r="J31" t="n">
-        <v>81.2594985928</v>
+        <v>82.0144907824</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3251,46 +3067,40 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="V31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="W31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="X31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.01527777777777774</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3409090909090915</v>
+        <v>0.2749999999999994</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01893939393939397</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.3409090909090915</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.01893939393939397</v>
+        <v>0.01527777777777774</v>
       </c>
     </row>
     <row r="32">
@@ -3300,13 +3110,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>5.12</v>
       </c>
       <c r="C32" t="n">
         <v>8.828209301999999</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>5.12</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3321,10 +3131,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I32" t="n">
-        <v>1267.447630053</v>
+        <v>1278.772512897</v>
       </c>
       <c r="J32" t="n">
-        <v>84.49650867019999</v>
+        <v>85.25150085979999</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3342,46 +3152,40 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="S32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="U32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="V32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="W32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="X32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.01388888888888885</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3181818181818188</v>
+        <v>0.2499999999999994</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.01767676767676771</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.3181818181818188</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.01767676767676771</v>
+        <v>0.01388888888888885</v>
       </c>
     </row>
     <row r="33">
@@ -3391,13 +3195,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>7.07</v>
       </c>
       <c r="C33" t="n">
         <v>8.488635288000001</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>7.07</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3412,10 +3216,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I33" t="n">
-        <v>1314.135124137</v>
+        <v>1325.460006981</v>
       </c>
       <c r="J33" t="n">
-        <v>87.60900827579999</v>
+        <v>88.3640004654</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3433,46 +3237,40 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="V33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.01249999999999996</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2954545454545461</v>
+        <v>0.2249999999999994</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01641414141414145</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.2954545454545461</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.01641414141414145</v>
+        <v>0.01249999999999996</v>
       </c>
     </row>
     <row r="34">
@@ -3482,13 +3280,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.66</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
         <v>8.293957799999999</v>
       </c>
       <c r="D34" t="n">
-        <v>8.66</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3503,10 +3301,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I34" t="n">
-        <v>1359.751892037</v>
+        <v>1371.076774881</v>
       </c>
       <c r="J34" t="n">
-        <v>90.65012613579999</v>
+        <v>91.4051183254</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3524,46 +3322,40 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="S34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.01111111111111108</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.2727272727272734</v>
+        <v>0.1999999999999994</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.01515151515151519</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.2727272727272734</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.01515151515151519</v>
+        <v>0.01111111111111108</v>
       </c>
     </row>
     <row r="35">
@@ -3573,13 +3365,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.92</v>
+        <v>7.01</v>
       </c>
       <c r="C35" t="n">
         <v>7.991015621999999</v>
       </c>
       <c r="D35" t="n">
-        <v>8.92</v>
+        <v>7.01</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3594,10 +3386,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I35" t="n">
-        <v>1403.702477958</v>
+        <v>1415.027360802</v>
       </c>
       <c r="J35" t="n">
-        <v>93.58016519719999</v>
+        <v>94.33515738679999</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3615,46 +3407,40 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="R35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="V35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="W35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="X35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.009722222222222188</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.2500000000000007</v>
+        <v>0.1749999999999994</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.01388888888888893</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.2500000000000007</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.01388888888888893</v>
+        <v>0.009722222222222188</v>
       </c>
     </row>
     <row r="36">
@@ -3664,13 +3450,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.42</v>
+        <v>7.34</v>
       </c>
       <c r="C36" t="n">
         <v>7.540579638</v>
       </c>
       <c r="D36" t="n">
-        <v>8.42</v>
+        <v>7.34</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3685,10 +3471,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I36" t="n">
-        <v>1445.175665967</v>
+        <v>1456.500548811</v>
       </c>
       <c r="J36" t="n">
-        <v>96.3450443978</v>
+        <v>97.10003658740001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3706,46 +3492,40 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="R36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="V36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.008333333333333299</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2272727272727279</v>
+        <v>0.1499999999999994</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01262626262626266</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.2272727272727279</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.01262626262626266</v>
+        <v>0.008333333333333299</v>
       </c>
     </row>
     <row r="37">
@@ -3755,13 +3535,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="C37" t="n">
         <v>7.111894061999999</v>
       </c>
       <c r="D37" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3776,10 +3556,10 @@
         <v>10.71383316875001</v>
       </c>
       <c r="I37" t="n">
-        <v>1484.291083308</v>
+        <v>1495.615966152</v>
       </c>
       <c r="J37" t="n">
-        <v>98.9527388872</v>
+        <v>99.7077310768</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3797,46 +3577,40 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="R37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="S37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="T37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="U37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="V37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="W37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="X37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.00694444444444441</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2045454545454552</v>
+        <v>0.1249999999999994</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.0113636363636364</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.2045454545454552</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.0113636363636364</v>
+        <v>0.00694444444444441</v>
       </c>
     </row>
     <row r="38">
@@ -3846,25 +3620,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8.92</v>
+        <v>9.02</v>
       </c>
       <c r="C38" t="n">
         <v>6.46511355</v>
       </c>
       <c r="D38" t="n">
-        <v>8.92</v>
+        <v>9.02</v>
       </c>
       <c r="E38" t="n">
-        <v>3.608946878727272</v>
+        <v>5.668016486727282</v>
       </c>
       <c r="F38" t="n">
-        <v>2.856166671272728</v>
+        <v>0.7970970632727172</v>
       </c>
       <c r="G38" t="n">
-        <v>24.14473152834091</v>
+        <v>24.16618017009091</v>
       </c>
       <c r="H38" t="n">
-        <v>14.47315283409091</v>
+        <v>16.61801700909092</v>
       </c>
       <c r="I38" t="n">
         <v>1500</v>
@@ -3879,55 +3653,49 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>62.83566676800001</v>
+        <v>17.53613539199978</v>
       </c>
       <c r="N38" t="n">
-        <v>-62.83566676800001</v>
+        <v>-17.53613539199978</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="S38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="V38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="W38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="X38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.005555555555555522</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.1818181818181825</v>
+        <v>0.09999999999999939</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.01010101010101014</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.1818181818181825</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.01010101010101014</v>
+        <v>0.005555555555555522</v>
       </c>
     </row>
     <row r="39">
@@ -3937,13 +3705,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>8.43</v>
       </c>
       <c r="C39" t="n">
         <v>6.164418432000001</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8.43</v>
       </c>
       <c r="E39" t="n">
         <v>6.164418432000001</v>
@@ -3952,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>24.20894422034091</v>
+        <v>24.23039286209091</v>
       </c>
       <c r="H39" t="n">
-        <v>20.89442203409092</v>
+        <v>23.03928620909092</v>
       </c>
       <c r="I39" t="n">
         <v>1500</v>
@@ -3979,46 +3747,40 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="S39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="V39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="W39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="X39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.004166666666666634</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.1590909090909097</v>
+        <v>0.0749999999999994</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.008838383838383874</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.1590909090909097</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.008838383838383874</v>
+        <v>0.004166666666666634</v>
       </c>
     </row>
     <row r="40">
@@ -4028,13 +3790,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="C40" t="n">
         <v>5.67882495</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="E40" t="n">
         <v>5.67882495</v>
@@ -4043,10 +3805,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>24.26809864690341</v>
+        <v>24.28954728865341</v>
       </c>
       <c r="H40" t="n">
-        <v>26.80986469034091</v>
+        <v>28.95472886534093</v>
       </c>
       <c r="I40" t="n">
         <v>1500</v>
@@ -4070,46 +3832,40 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.04999999999999939</v>
       </c>
       <c r="R40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="S40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.04999999999999939</v>
       </c>
       <c r="T40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="U40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.04999999999999939</v>
       </c>
       <c r="V40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="W40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.04999999999999939</v>
       </c>
       <c r="X40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.002777777777777744</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.136363636363637</v>
+        <v>0.0499999999999994</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.007575757575757611</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.136363636363637</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.007575757575757611</v>
+        <v>0.002777777777777744</v>
       </c>
     </row>
     <row r="41">
@@ -4119,13 +3875,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8.9</v>
+        <v>10.23</v>
       </c>
       <c r="C41" t="n">
         <v>4.970956512</v>
       </c>
       <c r="D41" t="n">
-        <v>8.9</v>
+        <v>10.23</v>
       </c>
       <c r="E41" t="n">
         <v>4.970956512</v>
@@ -4134,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>24.31987944390341</v>
+        <v>24.34132808565341</v>
       </c>
       <c r="H41" t="n">
-        <v>31.98794439034091</v>
+        <v>34.13280856534093</v>
       </c>
       <c r="I41" t="n">
         <v>1500</v>
@@ -4161,46 +3917,40 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="S41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="V41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="W41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="X41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.001388888888888855</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.1136363636363643</v>
+        <v>0.0249999999999994</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.006313131313131349</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.1136363636363643</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.006313131313131349</v>
+        <v>0.001388888888888855</v>
       </c>
     </row>
     <row r="42">
@@ -4210,13 +3960,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.25</v>
+        <v>9.42</v>
       </c>
       <c r="C42" t="n">
         <v>4.457903022000001</v>
       </c>
       <c r="D42" t="n">
-        <v>8.25</v>
+        <v>9.42</v>
       </c>
       <c r="E42" t="n">
         <v>4.457903022000001</v>
@@ -4225,10 +3975,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>24.36631593371591</v>
+        <v>24.38776457546591</v>
       </c>
       <c r="H42" t="n">
-        <v>36.63159337159091</v>
+        <v>38.77645754659093</v>
       </c>
       <c r="I42" t="n">
         <v>1500</v>
@@ -4252,46 +4002,40 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.09090909090909152</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.09090909090909155</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.005050505050505086</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.09090909090909155</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.005050505050505086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4301,31 +4045,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.42</v>
+        <v>9.41</v>
       </c>
       <c r="C43" t="n">
         <v>3.797568287999999</v>
       </c>
       <c r="D43" t="n">
-        <v>8.42</v>
+        <v>9.41</v>
       </c>
       <c r="E43" t="n">
-        <v>3.797568287999999</v>
+        <v>-5.202431712000001</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>24.40587393671591</v>
+        <v>24.33357257846591</v>
       </c>
       <c r="H43" t="n">
-        <v>40.58739367159091</v>
+        <v>33.35725784659093</v>
       </c>
       <c r="I43" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -4334,55 +4078,49 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4198</v>
       </c>
       <c r="P43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0.06818181818181879</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>0.06818181818181879</v>
+        <v>0.1804166666666667</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.06818181818181879</v>
+        <v>0.01002314814814815</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.06818181818181883</v>
+        <v>0.1804166666666667</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.003787878787878824</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.06818181818181883</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.003787878787878824</v>
+        <v>0.01002314814814815</v>
       </c>
     </row>
     <row r="44">
@@ -4392,31 +4130,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8.369999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="C44" t="n">
         <v>3.29000595</v>
       </c>
       <c r="D44" t="n">
-        <v>8.369999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="E44" t="n">
-        <v>3.29000595</v>
+        <v>-5.70999405</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>24.44014483202841</v>
+        <v>24.27409347377841</v>
       </c>
       <c r="H44" t="n">
-        <v>44.01448320284091</v>
+        <v>27.40934737784093</v>
       </c>
       <c r="I44" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4425,55 +4163,49 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2198</v>
       </c>
       <c r="P44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0.04545454545454606</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04545454545454606</v>
+        <v>0.3330555555555555</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.04545454545454606</v>
+        <v>0.01850308641975309</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.04545454545454611</v>
+        <v>0.3330555555555555</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.002525252525252561</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.04545454545454611</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.002525252525252561</v>
+        <v>0.01850308641975309</v>
       </c>
     </row>
     <row r="45">
@@ -4483,31 +4215,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8.039999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="C45" t="n">
         <v>2.612099328</v>
       </c>
       <c r="D45" t="n">
-        <v>8.039999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="E45" t="n">
-        <v>2.612099328</v>
+        <v>-6.387900672</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>24.46735420002841</v>
+        <v>24.20755284177841</v>
       </c>
       <c r="H45" t="n">
-        <v>46.73542000284091</v>
+        <v>20.75528417784093</v>
       </c>
       <c r="I45" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4516,55 +4248,49 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="P45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0.02272727272727333</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0.02272727272727333</v>
+        <v>0.3468055555555555</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.02272727272727333</v>
+        <v>0.01926697530864198</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.02272727272727338</v>
+        <v>0.3468055555555555</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.001262626262626299</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.01926697530864198</v>
       </c>
     </row>
     <row r="46">
@@ -4574,13 +4300,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8.31</v>
+        <v>9.33</v>
       </c>
       <c r="C46" t="n">
         <v>2.000548902</v>
       </c>
       <c r="D46" t="n">
-        <v>8.31</v>
+        <v>9.33</v>
       </c>
       <c r="E46" t="n">
         <v>-6.999451098</v>
@@ -4589,16 +4315,16 @@
         <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>24.39444325109091</v>
+        <v>24.13464189284091</v>
       </c>
       <c r="H46" t="n">
-        <v>39.44432510909091</v>
+        <v>13.46418928409093</v>
       </c>
       <c r="I46" t="n">
-        <v>499.9999999999995</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4610,10 +4336,10 @@
         <v>198</v>
       </c>
       <c r="N46" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4198</v>
+        <v>198</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -4640,22 +4366,16 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0.3605555555555555</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0.02003086419753086</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.3343181818181827</v>
+        <v>0.3605555555555555</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01857323232323237</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02003086419753086</v>
       </c>
     </row>
     <row r="47">
@@ -4665,13 +4385,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="C47" t="n">
         <v>1.358764782</v>
       </c>
       <c r="D47" t="n">
-        <v>7.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="E47" t="n">
         <v>-7.641235218</v>
@@ -4680,10 +4400,10 @@
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>24.31484705090341</v>
+        <v>24.05504569265341</v>
       </c>
       <c r="H47" t="n">
-        <v>31.48470509034091</v>
+        <v>5.504569265340926</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -4701,10 +4421,10 @@
         <v>198</v>
       </c>
       <c r="N47" t="n">
-        <v>1999.999999999998</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2197.999999999998</v>
+        <v>198</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -4731,22 +4451,16 @@
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0.3743055555555555</v>
       </c>
       <c r="Y47" t="n">
-        <v>1</v>
+        <v>0.02079475308641975</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.6395959595959603</v>
+        <v>0.3743055555555555</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.03553310886644224</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02079475308641975</v>
       </c>
     </row>
     <row r="48">
@@ -4756,25 +4470,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6.48</v>
+        <v>7.33</v>
       </c>
       <c r="C48" t="n">
         <v>0.6906375119999999</v>
       </c>
       <c r="D48" t="n">
-        <v>6.48</v>
+        <v>10.35497599327271</v>
       </c>
       <c r="E48" t="n">
-        <v>-8.309362488</v>
+        <v>-5.28438649472729</v>
       </c>
       <c r="F48" t="n">
         <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>24.22829119165341</v>
+        <v>24</v>
       </c>
       <c r="H48" t="n">
-        <v>22.82911916534091</v>
+        <v>-6.938893903907228e-16</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -4822,22 +4536,16 @@
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0.3880555555555555</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>0.02155864197530864</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.6670959595959602</v>
+        <v>0.3880555555555555</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.03706088664422001</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02155864197530864</v>
       </c>
     </row>
     <row r="49">
@@ -4847,25 +4555,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7.34</v>
+        <v>7.28</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>7.34</v>
+        <v>16.28</v>
       </c>
       <c r="E49" t="n">
-        <v>-9</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="F49" t="n">
         <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>24.13454119165341</v>
+        <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>13.45411916534091</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4913,22 +4621,16 @@
         <v>1</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0.4018055555555555</v>
       </c>
       <c r="Y49" t="n">
-        <v>1</v>
+        <v>0.02232253086419753</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.6945959595959602</v>
+        <v>0.4018055555555555</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.03858866442199779</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02232253086419753</v>
       </c>
     </row>
     <row r="50">
@@ -4938,25 +4640,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6.5</v>
+        <v>5.52</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>6.5</v>
+        <v>14.52</v>
       </c>
       <c r="E50" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>24.04079119165341</v>
+        <v>24</v>
       </c>
       <c r="H50" t="n">
-        <v>4.079119165340911</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -5004,22 +4706,16 @@
         <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0.4155555555555555</v>
       </c>
       <c r="Y50" t="n">
-        <v>1</v>
+        <v>0.02308641975308641</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.7220959595959602</v>
+        <v>0.4155555555555555</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.04011644219977557</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02308641975308641</v>
       </c>
     </row>
     <row r="51">
@@ -5029,16 +4725,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.29</v>
+        <v>7.11</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>11.37404560127273</v>
+        <v>16.11</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.915954398727274</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>9</v>
@@ -5095,22 +4791,16 @@
         <v>1</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0.4293055555555554</v>
       </c>
       <c r="Y51" t="n">
-        <v>1</v>
+        <v>0.0238503086419753</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.7495959595959601</v>
+        <v>0.4293055555555554</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.04164421997755334</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.0238503086419753</v>
       </c>
     </row>
     <row r="52">
@@ -5120,13 +4810,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5.72</v>
+        <v>6.17</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>14.72</v>
+        <v>15.17</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -5186,22 +4876,16 @@
         <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0.4430555555555554</v>
       </c>
       <c r="Y52" t="n">
-        <v>1</v>
+        <v>0.02461419753086419</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.7770959595959601</v>
+        <v>0.4430555555555554</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.04317199775533112</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02461419753086419</v>
       </c>
     </row>
     <row r="53">
@@ -5211,13 +4895,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5.13</v>
+        <v>7.12</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>14.13</v>
+        <v>16.12</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -5277,22 +4961,16 @@
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>0.4568055555555554</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>0.02537808641975308</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.8045959595959601</v>
+        <v>0.4568055555555554</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.04469977553310889</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02537808641975308</v>
       </c>
     </row>
     <row r="54">
@@ -5302,13 +4980,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5.87</v>
+        <v>6.19</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>14.87</v>
+        <v>15.19</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -5368,22 +5046,16 @@
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>0.4705555555555554</v>
       </c>
       <c r="Y54" t="n">
-        <v>1</v>
+        <v>0.02614197530864196</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.8320959595959601</v>
+        <v>0.4705555555555554</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.04622755331088667</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02614197530864196</v>
       </c>
     </row>
     <row r="55">
@@ -5393,13 +5065,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4.85</v>
+        <v>7.02</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>13.85</v>
+        <v>16.02</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -5459,22 +5131,16 @@
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>0.4843055555555554</v>
       </c>
       <c r="Y55" t="n">
-        <v>1</v>
+        <v>0.02690586419753085</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.85959595959596</v>
+        <v>0.4843055555555554</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.04775533108866445</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02690586419753085</v>
       </c>
     </row>
     <row r="56">
@@ -5484,13 +5150,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -5550,22 +5216,16 @@
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0.4980555555555554</v>
       </c>
       <c r="Y56" t="n">
-        <v>1</v>
+        <v>0.02766975308641974</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.88709595959596</v>
+        <v>0.4980555555555554</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.04928310886644223</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02766975308641974</v>
       </c>
     </row>
     <row r="57">
@@ -5575,13 +5235,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.78</v>
+        <v>6.22</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>13.78</v>
+        <v>15.22</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -5641,22 +5301,16 @@
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>0.5118055555555554</v>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>0.02843364197530864</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.91459595959596</v>
+        <v>0.5118055555555554</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.05081088664422</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02843364197530864</v>
       </c>
     </row>
     <row r="58">
@@ -5666,13 +5320,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4.06</v>
+        <v>9.06</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>13.06</v>
+        <v>18.06</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -5732,22 +5386,16 @@
         <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>0.5255555555555554</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>0.02919753086419753</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.9420959595959599</v>
+        <v>0.5255555555555554</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.05233866442199778</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02919753086419753</v>
       </c>
     </row>
     <row r="59">
@@ -5757,13 +5405,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.47</v>
+        <v>9.02</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>12.47</v>
+        <v>18.02</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -5823,22 +5471,16 @@
         <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>1</v>
+        <v>0.5393055555555555</v>
       </c>
       <c r="Y59" t="n">
-        <v>1</v>
+        <v>0.02996141975308641</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.9695959595959599</v>
+        <v>0.5393055555555555</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.05386644219977555</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.02996141975308641</v>
       </c>
     </row>
     <row r="60">
@@ -5848,13 +5490,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.29</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>12.29</v>
+        <v>18.3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -5914,22 +5556,16 @@
         <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>1</v>
+        <v>0.5530555555555555</v>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>0.03072530864197531</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.9970959595959599</v>
+        <v>0.5530555555555555</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.05539421997755332</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0.02272727272727338</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0.001262626262626299</v>
+        <v>0.03072530864197531</v>
       </c>
     </row>
     <row r="61">
@@ -5939,13 +5575,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.8</v>
+        <v>9.35</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>18.35</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -6005,22 +5641,16 @@
         <v>1</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>0.5668055555555556</v>
       </c>
       <c r="Y61" t="n">
-        <v>1</v>
+        <v>0.0314891975308642</v>
       </c>
       <c r="Z61" t="n">
-        <v>1</v>
+        <v>0.5668055555555556</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0.04732323232323325</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0.002629068462401847</v>
+        <v>0.0314891975308642</v>
       </c>
     </row>
     <row r="62">
@@ -6030,13 +5660,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.5</v>
+        <v>9.49</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>18.49</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -6096,22 +5726,16 @@
         <v>1</v>
       </c>
       <c r="X62" t="n">
-        <v>1</v>
+        <v>0.5805555555555556</v>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>0.03225308641975309</v>
       </c>
       <c r="Z62" t="n">
-        <v>1</v>
+        <v>0.5805555555555556</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0.07482323232323325</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0.004156846240179625</v>
+        <v>0.03225308641975309</v>
       </c>
     </row>
     <row r="63">
@@ -6121,13 +5745,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.79</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>11.79</v>
+        <v>18.55</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -6187,22 +5811,16 @@
         <v>1</v>
       </c>
       <c r="X63" t="n">
-        <v>1</v>
+        <v>0.5943055555555556</v>
       </c>
       <c r="Y63" t="n">
-        <v>1</v>
+        <v>0.03301697530864198</v>
       </c>
       <c r="Z63" t="n">
-        <v>1</v>
+        <v>0.5943055555555556</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0.1023232323232332</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0.005684624017957403</v>
+        <v>0.03301697530864198</v>
       </c>
     </row>
     <row r="64">
@@ -6212,13 +5830,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>12.15</v>
+        <v>18.11</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -6278,22 +5896,16 @@
         <v>1</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
+        <v>0.6080555555555557</v>
       </c>
       <c r="Y64" t="n">
-        <v>1</v>
+        <v>0.03378086419753087</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
+        <v>0.6080555555555557</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0.1298232323232333</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0.007212401795735181</v>
+        <v>0.03378086419753087</v>
       </c>
     </row>
     <row r="65">
@@ -6303,13 +5915,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.31</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>11.31</v>
+        <v>18.39</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -6369,22 +5981,16 @@
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>1</v>
+        <v>0.6218055555555557</v>
       </c>
       <c r="Y65" t="n">
-        <v>1</v>
+        <v>0.03454475308641976</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
+        <v>0.6218055555555557</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0.1573232323232333</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0.008740179573512958</v>
+        <v>0.03454475308641976</v>
       </c>
     </row>
     <row r="66">
@@ -6394,13 +6000,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.8</v>
+        <v>8.35</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>17.35</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -6460,22 +6066,16 @@
         <v>1</v>
       </c>
       <c r="X66" t="n">
-        <v>1</v>
+        <v>0.6355555555555558</v>
       </c>
       <c r="Y66" t="n">
-        <v>1</v>
+        <v>0.03530864197530866</v>
       </c>
       <c r="Z66" t="n">
-        <v>1</v>
+        <v>0.6355555555555558</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0.1848232323232332</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0.01026795735129074</v>
+        <v>0.03530864197530866</v>
       </c>
     </row>
     <row r="67">
@@ -6485,13 +6085,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.16</v>
+        <v>8.25</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>12.16</v>
+        <v>17.25</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -6551,22 +6151,16 @@
         <v>1</v>
       </c>
       <c r="X67" t="n">
-        <v>1</v>
+        <v>0.6493055555555558</v>
       </c>
       <c r="Y67" t="n">
-        <v>1</v>
+        <v>0.03607253086419755</v>
       </c>
       <c r="Z67" t="n">
-        <v>1</v>
+        <v>0.6493055555555558</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0.2123232323232332</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0.01179573512906851</v>
+        <v>0.03607253086419755</v>
       </c>
     </row>
     <row r="68">
@@ -6576,13 +6170,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.61</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>11.61</v>
+        <v>17.13</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -6642,22 +6236,16 @@
         <v>1</v>
       </c>
       <c r="X68" t="n">
-        <v>1</v>
+        <v>0.6630555555555558</v>
       </c>
       <c r="Y68" t="n">
-        <v>1</v>
+        <v>0.03683641975308644</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
+        <v>0.6630555555555558</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0.2398232323232332</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0.01332351290684629</v>
+        <v>0.03683641975308644</v>
       </c>
     </row>
     <row r="69">
@@ -6667,13 +6255,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3.11</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>12.11</v>
+        <v>17.29</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -6733,22 +6321,16 @@
         <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>1</v>
+        <v>0.6768055555555559</v>
       </c>
       <c r="Y69" t="n">
-        <v>1</v>
+        <v>0.03760030864197533</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>0.6768055555555559</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0.2673232323232332</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0.01485129068462407</v>
+        <v>0.03760030864197533</v>
       </c>
     </row>
     <row r="70">
@@ -6758,13 +6340,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.33</v>
+        <v>6.35</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>11.33</v>
+        <v>15.35</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -6824,22 +6406,16 @@
         <v>1</v>
       </c>
       <c r="X70" t="n">
-        <v>1</v>
+        <v>0.6905555555555559</v>
       </c>
       <c r="Y70" t="n">
-        <v>1</v>
+        <v>0.03836419753086422</v>
       </c>
       <c r="Z70" t="n">
-        <v>1</v>
+        <v>0.6905555555555559</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0.2948232323232333</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0.01637906846240185</v>
+        <v>0.03836419753086422</v>
       </c>
     </row>
     <row r="71">
@@ -6849,13 +6425,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3.1</v>
+        <v>5.43</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>12.1</v>
+        <v>14.43</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -6915,22 +6491,16 @@
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>1</v>
+        <v>0.704305555555556</v>
       </c>
       <c r="Y71" t="n">
-        <v>1</v>
+        <v>0.03912808641975311</v>
       </c>
       <c r="Z71" t="n">
-        <v>1</v>
+        <v>0.704305555555556</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0.3223232323232333</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0.01790684624017963</v>
+        <v>0.03912808641975311</v>
       </c>
     </row>
     <row r="72">
@@ -6940,13 +6510,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.84</v>
+        <v>6.28</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>11.84</v>
+        <v>15.28</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -7006,22 +6576,16 @@
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>1</v>
+        <v>0.718055555555556</v>
       </c>
       <c r="Y72" t="n">
-        <v>1</v>
+        <v>0.039891975308642</v>
       </c>
       <c r="Z72" t="n">
-        <v>1</v>
+        <v>0.718055555555556</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0.3498232323232333</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0.01943462401795741</v>
+        <v>0.039891975308642</v>
       </c>
     </row>
     <row r="73">
@@ -7031,13 +6595,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.31</v>
+        <v>6.44</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>11.31</v>
+        <v>15.44</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -7097,22 +6661,16 @@
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>1</v>
+        <v>0.731805555555556</v>
       </c>
       <c r="Y73" t="n">
-        <v>1</v>
+        <v>0.04065586419753089</v>
       </c>
       <c r="Z73" t="n">
-        <v>1</v>
+        <v>0.731805555555556</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0.3773232323232333</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0.02096240179573518</v>
+        <v>0.04065586419753089</v>
       </c>
     </row>
     <row r="74">
@@ -7122,13 +6680,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.52</v>
+        <v>6.05</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>11.52</v>
+        <v>15.05</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -7188,22 +6746,16 @@
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>1</v>
+        <v>0.7455555555555561</v>
       </c>
       <c r="Y74" t="n">
-        <v>1</v>
+        <v>0.04141975308641978</v>
       </c>
       <c r="Z74" t="n">
-        <v>1</v>
+        <v>0.7455555555555561</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0.4048232323232334</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0.02249017957351297</v>
+        <v>0.04141975308641978</v>
       </c>
     </row>
     <row r="75">
@@ -7213,13 +6765,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3.34</v>
+        <v>1.55</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>12.34</v>
+        <v>10.55</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -7279,22 +6831,16 @@
         <v>1</v>
       </c>
       <c r="X75" t="n">
-        <v>1</v>
+        <v>0.7593055555555561</v>
       </c>
       <c r="Y75" t="n">
-        <v>1</v>
+        <v>0.04218364197530867</v>
       </c>
       <c r="Z75" t="n">
-        <v>1</v>
+        <v>0.7593055555555561</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0.4323232323232334</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0.02401795735129075</v>
+        <v>0.04218364197530867</v>
       </c>
     </row>
     <row r="76">
@@ -7304,13 +6850,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>11.31</v>
+        <v>10.39</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -7370,22 +6916,16 @@
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>1</v>
+        <v>0.7730555555555562</v>
       </c>
       <c r="Y76" t="n">
-        <v>1</v>
+        <v>0.04294753086419757</v>
       </c>
       <c r="Z76" t="n">
-        <v>1</v>
+        <v>0.7730555555555562</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0.4598232323232334</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>0.02554573512906852</v>
+        <v>0.04294753086419757</v>
       </c>
     </row>
     <row r="77">
@@ -7395,13 +6935,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2.57</v>
+        <v>1.3</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>11.57</v>
+        <v>10.3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -7461,22 +7001,16 @@
         <v>1</v>
       </c>
       <c r="X77" t="n">
-        <v>1</v>
+        <v>0.7868055555555562</v>
       </c>
       <c r="Y77" t="n">
-        <v>1</v>
+        <v>0.04371141975308646</v>
       </c>
       <c r="Z77" t="n">
-        <v>1</v>
+        <v>0.7868055555555562</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0.4873232323232334</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0.0270735129068463</v>
+        <v>0.04371141975308646</v>
       </c>
     </row>
     <row r="78">
@@ -7486,13 +7020,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>12.2</v>
+        <v>10.45</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -7552,22 +7086,16 @@
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>1</v>
+        <v>0.8005555555555562</v>
       </c>
       <c r="Y78" t="n">
-        <v>1</v>
+        <v>0.04447530864197535</v>
       </c>
       <c r="Z78" t="n">
-        <v>1</v>
+        <v>0.8005555555555562</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0.5148232323232335</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0.02860129068462408</v>
+        <v>0.04447530864197535</v>
       </c>
     </row>
     <row r="79">
@@ -7577,13 +7105,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>11.41</v>
+        <v>10.52</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -7643,22 +7171,16 @@
         <v>1</v>
       </c>
       <c r="X79" t="n">
-        <v>1</v>
+        <v>0.8143055555555563</v>
       </c>
       <c r="Y79" t="n">
-        <v>1</v>
+        <v>0.04523919753086424</v>
       </c>
       <c r="Z79" t="n">
-        <v>1</v>
+        <v>0.8143055555555563</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0.5423232323232334</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0.03012906846240185</v>
+        <v>0.04523919753086424</v>
       </c>
     </row>
     <row r="80">
@@ -7668,13 +7190,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>11.48</v>
+        <v>11.05</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -7734,22 +7256,16 @@
         <v>1</v>
       </c>
       <c r="X80" t="n">
-        <v>1</v>
+        <v>0.8280555555555563</v>
       </c>
       <c r="Y80" t="n">
-        <v>1</v>
+        <v>0.04600308641975313</v>
       </c>
       <c r="Z80" t="n">
-        <v>1</v>
+        <v>0.8280555555555563</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>0.5698232323232334</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>0.03165684624017963</v>
+        <v>0.04600308641975313</v>
       </c>
     </row>
     <row r="81">
@@ -7759,13 +7275,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2.7</v>
+        <v>1.39</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>11.7</v>
+        <v>10.39</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -7825,22 +7341,16 @@
         <v>1</v>
       </c>
       <c r="X81" t="n">
-        <v>1</v>
+        <v>0.8418055555555564</v>
       </c>
       <c r="Y81" t="n">
-        <v>1</v>
+        <v>0.04676697530864202</v>
       </c>
       <c r="Z81" t="n">
-        <v>1</v>
+        <v>0.8418055555555564</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>0.5973232323232334</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>0.03318462401795741</v>
+        <v>0.04676697530864202</v>
       </c>
     </row>
     <row r="82">
@@ -7850,13 +7360,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>12.28</v>
+        <v>11.05</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -7916,22 +7426,16 @@
         <v>1</v>
       </c>
       <c r="X82" t="n">
-        <v>1</v>
+        <v>0.8555555555555564</v>
       </c>
       <c r="Y82" t="n">
-        <v>1</v>
+        <v>0.04753086419753091</v>
       </c>
       <c r="Z82" t="n">
-        <v>1</v>
+        <v>0.8555555555555564</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0.6248232323232333</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0.03471240179573518</v>
+        <v>0.04753086419753091</v>
       </c>
     </row>
     <row r="83">
@@ -7941,13 +7445,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>11.5</v>
+        <v>10.52</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -8007,22 +7511,16 @@
         <v>1</v>
       </c>
       <c r="X83" t="n">
-        <v>1</v>
+        <v>0.8693055555555564</v>
       </c>
       <c r="Y83" t="n">
-        <v>1</v>
+        <v>0.0482947530864198</v>
       </c>
       <c r="Z83" t="n">
-        <v>1</v>
+        <v>0.8693055555555564</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0.6523232323232333</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0.03624017957351296</v>
+        <v>0.0482947530864198</v>
       </c>
     </row>
     <row r="84">
@@ -8032,13 +7530,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.57</v>
+        <v>1.45</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>11.57</v>
+        <v>10.45</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -8098,22 +7596,16 @@
         <v>1</v>
       </c>
       <c r="X84" t="n">
-        <v>1</v>
+        <v>0.8830555555555565</v>
       </c>
       <c r="Y84" t="n">
-        <v>1</v>
+        <v>0.04905864197530869</v>
       </c>
       <c r="Z84" t="n">
-        <v>1</v>
+        <v>0.8830555555555565</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>0.6798232323232333</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>0.03776795735129074</v>
+        <v>0.04905864197530869</v>
       </c>
     </row>
     <row r="85">
@@ -8123,13 +7615,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.57</v>
+        <v>1.42</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>11.57</v>
+        <v>10.42</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -8189,22 +7681,16 @@
         <v>1</v>
       </c>
       <c r="X85" t="n">
-        <v>1</v>
+        <v>0.8968055555555565</v>
       </c>
       <c r="Y85" t="n">
-        <v>1</v>
+        <v>0.04982253086419759</v>
       </c>
       <c r="Z85" t="n">
-        <v>1</v>
+        <v>0.8968055555555565</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0.7073232323232332</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>0.03929573512906851</v>
+        <v>0.04982253086419759</v>
       </c>
     </row>
     <row r="86">
@@ -8214,13 +7700,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3.54</v>
+        <v>1.52</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>12.54</v>
+        <v>10.52</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -8280,22 +7766,16 @@
         <v>1</v>
       </c>
       <c r="X86" t="n">
-        <v>1</v>
+        <v>0.9105555555555566</v>
       </c>
       <c r="Y86" t="n">
-        <v>1</v>
+        <v>0.05058641975308648</v>
       </c>
       <c r="Z86" t="n">
-        <v>1</v>
+        <v>0.9105555555555566</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>0.7348232323232332</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>0.04082351290684629</v>
+        <v>0.05058641975308648</v>
       </c>
     </row>
     <row r="87">
@@ -8305,13 +7785,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3.54</v>
+        <v>2.08</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>12.54</v>
+        <v>11.08</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -8371,22 +7851,16 @@
         <v>1</v>
       </c>
       <c r="X87" t="n">
-        <v>1</v>
+        <v>0.9243055555555566</v>
       </c>
       <c r="Y87" t="n">
-        <v>1</v>
+        <v>0.05135030864197537</v>
       </c>
       <c r="Z87" t="n">
-        <v>1</v>
+        <v>0.9243055555555566</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>0.7623232323232332</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>0.04235129068462407</v>
+        <v>0.05135030864197537</v>
       </c>
     </row>
     <row r="88">
@@ -8396,13 +7870,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>12.1</v>
+        <v>10.33</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -8462,22 +7936,16 @@
         <v>1</v>
       </c>
       <c r="X88" t="n">
-        <v>1</v>
+        <v>0.9380555555555566</v>
       </c>
       <c r="Y88" t="n">
-        <v>1</v>
+        <v>0.05211419753086426</v>
       </c>
       <c r="Z88" t="n">
-        <v>1</v>
+        <v>0.9380555555555566</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>0.7898232323232331</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>0.04387906846240185</v>
+        <v>0.05211419753086426</v>
       </c>
     </row>
     <row r="89">
@@ -8487,13 +7955,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.87</v>
+        <v>1.47</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>11.87</v>
+        <v>10.47</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -8553,22 +8021,16 @@
         <v>1</v>
       </c>
       <c r="X89" t="n">
-        <v>1</v>
+        <v>0.9518055555555567</v>
       </c>
       <c r="Y89" t="n">
-        <v>1</v>
+        <v>0.05287808641975315</v>
       </c>
       <c r="Z89" t="n">
-        <v>1</v>
+        <v>0.9518055555555567</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>0.8173232323232331</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>0.04540684624017962</v>
+        <v>0.05287808641975315</v>
       </c>
     </row>
     <row r="90">
@@ -8578,13 +8040,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>12</v>
+        <v>10.49</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -8644,22 +8106,16 @@
         <v>1</v>
       </c>
       <c r="X90" t="n">
-        <v>1</v>
+        <v>0.9655555555555567</v>
       </c>
       <c r="Y90" t="n">
-        <v>1</v>
+        <v>0.05364197530864204</v>
       </c>
       <c r="Z90" t="n">
-        <v>1</v>
+        <v>0.9655555555555567</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>0.8448232323232331</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>0.04693462401795739</v>
+        <v>0.05364197530864204</v>
       </c>
     </row>
     <row r="91">
@@ -8669,13 +8125,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.28</v>
+        <v>1.47</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>12.28</v>
+        <v>10.47</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -8735,22 +8191,16 @@
         <v>1</v>
       </c>
       <c r="X91" t="n">
-        <v>1</v>
+        <v>0.9793055555555568</v>
       </c>
       <c r="Y91" t="n">
-        <v>1</v>
+        <v>0.05440586419753093</v>
       </c>
       <c r="Z91" t="n">
-        <v>1</v>
+        <v>0.9793055555555568</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0.8723232323232331</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0.04846240179573517</v>
+        <v>0.05440586419753093</v>
       </c>
     </row>
     <row r="92">
@@ -8760,13 +8210,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2.39</v>
+        <v>1.51</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>11.39</v>
+        <v>10.51</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -8826,22 +8276,16 @@
         <v>1</v>
       </c>
       <c r="X92" t="n">
-        <v>1</v>
+        <v>0.9930555555555568</v>
       </c>
       <c r="Y92" t="n">
-        <v>1</v>
+        <v>0.05516975308641982</v>
       </c>
       <c r="Z92" t="n">
-        <v>1</v>
+        <v>0.9930555555555568</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0.899823232323233</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>0.04999017957351295</v>
+        <v>0.05516975308641982</v>
       </c>
     </row>
     <row r="93">
@@ -8851,19 +8295,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3.16</v>
+        <v>1.51</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>12.16</v>
+        <v>6.05545454545373</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>9</v>
+        <v>4.545454545453731</v>
       </c>
       <c r="G93" t="n">
         <v>24</v>
@@ -8884,13 +8328,13 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>198</v>
+        <v>99.99999999998207</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>198</v>
+        <v>99.99999999998207</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -8920,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="Y93" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z93" t="n">
         <v>1</v>
@@ -8928,12 +8372,6 @@
       <c r="AA93" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AB93" t="n">
-        <v>0.927323232323233</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>0.05151795735129072</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8942,19 +8380,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.31</v>
+        <v>1.45</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>11.31</v>
+        <v>1.45</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>24</v>
@@ -8975,13 +8413,13 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
@@ -9011,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="Y94" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z94" t="n">
         <v>1</v>
@@ -9019,12 +8457,6 @@
       <c r="AA94" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AB94" t="n">
-        <v>0.954823232323233</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>0.0530457351290685</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9033,19 +8465,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3.14</v>
+        <v>1.58</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>12.14</v>
+        <v>1.58</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>24</v>
@@ -9066,13 +8498,13 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -9102,7 +8534,7 @@
         <v>1</v>
       </c>
       <c r="Y95" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z95" t="n">
         <v>1</v>
@@ -9110,12 +8542,6 @@
       <c r="AA95" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AB95" t="n">
-        <v>0.9823232323232329</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>0.05457351290684627</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9124,19 +8550,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4.35</v>
+        <v>1.42</v>
       </c>
       <c r="C96" t="n">
         <v>0.6889206480000001</v>
       </c>
       <c r="D96" t="n">
-        <v>9.446203318941951</v>
+        <v>1.42</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>5.78512396694195</v>
+        <v>0.6889206480000001</v>
       </c>
       <c r="G96" t="n">
         <v>24</v>
@@ -9145,10 +8571,10 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>3.789063564000001</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>0.2526042376</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -9157,13 +8583,13 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>127.2727272727229</v>
+        <v>15.156254256</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>-15.156254256</v>
       </c>
       <c r="O96" t="n">
-        <v>127.2727272727229</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
         <v>1</v>
@@ -9193,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="Y96" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z96" t="n">
         <v>1</v>
@@ -9201,12 +8627,6 @@
       <c r="AA96" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AB96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0.05555555555555555</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9215,13 +8635,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4.14</v>
+        <v>1.56</v>
       </c>
       <c r="C97" t="n">
         <v>1.402933752</v>
       </c>
       <c r="D97" t="n">
-        <v>4.14</v>
+        <v>1.56</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -9236,10 +8656,10 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>7.716135635999999</v>
+        <v>11.5051992</v>
       </c>
       <c r="J97" t="n">
-        <v>0.5144090424</v>
+        <v>0.76701328</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -9284,18 +8704,12 @@
         <v>1</v>
       </c>
       <c r="Y97" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="Z97" t="n">
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC97" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
